--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_edge_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_edge_profile_summary.xlsx
@@ -437,7 +437,7 @@
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -549,25 +549,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>59.56000000000003</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>21.90541499999997</v>
+        <v>34.80403499999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9981515711645101</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="I2" t="n">
-        <v>19.54999999999999</v>
+        <v>-13.38700000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>85.11499999999999</v>
+        <v>70.47675000000002</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9981515711645101</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>70.68999999999998</v>
+        <v>-91.96000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>36.90191400000002</v>
+        <v>127.8779565</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8586792135775499</v>
+        <v>0.1776911733726564</v>
       </c>
       <c r="I3" t="n">
-        <v>-110.9</v>
+        <v>-350.886</v>
       </c>
       <c r="J3" t="n">
-        <v>104.7375</v>
+        <v>51.18175000000004</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8586792135775499</v>
+        <v>0.8223088266273436</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -667,25 +667,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-81.85499999999996</v>
+        <v>-97.04500000000002</v>
       </c>
       <c r="G4" t="n">
-        <v>43.51431000000003</v>
+        <v>25.59708900000002</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2221475382288691</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-123.91</v>
+        <v>-177.813</v>
       </c>
       <c r="J4" t="n">
-        <v>93.0325</v>
+        <v>-62.01474999999998</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7778524617711309</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-109.175</v>
+        <v>155.3800000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>56.25725699999999</v>
+        <v>164.8428809999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3085195765417577</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="I5" t="n">
-        <v>-164.3424999999999</v>
+        <v>-148.41225</v>
       </c>
       <c r="J5" t="n">
-        <v>269.505</v>
+        <v>283.62575</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6914804234582423</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -785,25 +785,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>26.77499999999999</v>
+        <v>54.27000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>34.61871000000001</v>
+        <v>23.38060200000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.838075004618511</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="I6" t="n">
-        <v>-12.81750000000002</v>
+        <v>13.31899999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>70.60625</v>
+        <v>84.059</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.838075004618511</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -844,25 +844,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-104.0475</v>
+        <v>61.20000000000002</v>
       </c>
       <c r="G7" t="n">
-        <v>140.9396625</v>
+        <v>51.07556999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1667282468132274</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="I7" t="n">
-        <v>-370.2225</v>
+        <v>-371.451</v>
       </c>
       <c r="J7" t="n">
-        <v>54.325</v>
+        <v>103.878</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8332717531867726</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-102.92</v>
+        <v>-89.66500000000002</v>
       </c>
       <c r="G8" t="n">
-        <v>31.63127100000003</v>
+        <v>53.82579300000009</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.1922349861858368</v>
       </c>
       <c r="I8" t="n">
-        <v>-206.10375</v>
+        <v>-212.26</v>
       </c>
       <c r="J8" t="n">
-        <v>-63.14375000000002</v>
+        <v>89.24200000000005</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.8077650138141632</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -962,25 +962,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>192.11</v>
+        <v>-73.69</v>
       </c>
       <c r="G9" t="n">
-        <v>115.7836469999999</v>
+        <v>131.017362</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7053389987068169</v>
+        <v>0.4561582085211575</v>
       </c>
       <c r="I9" t="n">
-        <v>-143.8325</v>
+        <v>-161.743</v>
       </c>
       <c r="J9" t="n">
-        <v>283.2</v>
+        <v>272.212</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7053389987068169</v>
+        <v>0.5438417914788425</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1021,25 +1021,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>66.595</v>
+        <v>64.69999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>35.300706</v>
+        <v>41.66847299999994</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6634304207119741</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="I10" t="n">
-        <v>-132.022</v>
+        <v>-132.525</v>
       </c>
       <c r="J10" t="n">
-        <v>95.95499999999998</v>
+        <v>96.30799999999999</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6634304207119741</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1080,25 +1080,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6.674999999999983</v>
+        <v>8.344999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>50.89024499999994</v>
+        <v>59.51156399999994</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5735623599701269</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="I11" t="n">
-        <v>-50.87000000000001</v>
+        <v>-49.76300000000003</v>
       </c>
       <c r="J11" t="n">
-        <v>169.583</v>
+        <v>171.043</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5735623599701269</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1139,19 +1139,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-90.55500000000001</v>
+        <v>-93.96000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>33.491934</v>
+        <v>32.12052899999998</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-133.516</v>
+        <v>-133.794</v>
       </c>
       <c r="J12" t="n">
-        <v>-54.47600000000001</v>
+        <v>-54.63499999999999</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-126.155</v>
+        <v>-123.655</v>
       </c>
       <c r="G13" t="n">
-        <v>43.97391600000004</v>
+        <v>45.67149300000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01493651979088872</v>
+        <v>0.01602136181575434</v>
       </c>
       <c r="I13" t="n">
-        <v>-181.629</v>
+        <v>-183.785</v>
       </c>
       <c r="J13" t="n">
-        <v>-67.16400000000002</v>
+        <v>-65.77200000000002</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9850634802091113</v>
+        <v>0.9839786381842457</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1257,25 +1257,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>37.52000000000001</v>
+        <v>50.25</v>
       </c>
       <c r="G14" t="n">
-        <v>60.94227300000002</v>
+        <v>45.29343000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6663267387313889</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="I14" t="n">
-        <v>-143.1545</v>
+        <v>-141.49</v>
       </c>
       <c r="J14" t="n">
-        <v>89.48000000000002</v>
+        <v>88.93499999999999</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6663267387313889</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1316,25 +1316,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-211.79</v>
+        <v>-166.58</v>
       </c>
       <c r="G15" t="n">
-        <v>193.427409</v>
+        <v>245.985579</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3408117479094432</v>
+        <v>0.3662426088514603</v>
       </c>
       <c r="I15" t="n">
-        <v>-353.6405</v>
+        <v>-350.97</v>
       </c>
       <c r="J15" t="n">
-        <v>180.034</v>
+        <v>177.515</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6591882520905568</v>
+        <v>0.6337573911485397</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-111.9</v>
+        <v>-108.48</v>
       </c>
       <c r="G16" t="n">
-        <v>23.528862</v>
+        <v>27.45033900000002</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-133.344</v>
+        <v>-132.78</v>
       </c>
       <c r="J16" t="n">
-        <v>-62.44250000000006</v>
+        <v>-60.76500000000001</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -1434,25 +1434,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-110.575</v>
+        <v>-114.2</v>
       </c>
       <c r="G17" t="n">
-        <v>32.50600499999993</v>
+        <v>34.80403499999995</v>
       </c>
       <c r="H17" t="n">
-        <v>0.006526616357332245</v>
+        <v>0.009496506002508511</v>
       </c>
       <c r="I17" t="n">
-        <v>-176.7795</v>
+        <v>-173.255</v>
       </c>
       <c r="J17" t="n">
-        <v>-71.06250000000001</v>
+        <v>-70.75999999999999</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9934733836426678</v>
+        <v>0.9905034939974915</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1493,25 +1493,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26.77499999999999</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
-        <v>34.61871000000001</v>
+        <v>34.80403499999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.838075004618511</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="I18" t="n">
-        <v>-12.81750000000002</v>
+        <v>-13.38700000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>70.60625</v>
+        <v>70.47675000000002</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.838075004618511</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1552,25 +1552,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-104.0475</v>
+        <v>-91.96000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>140.9396625</v>
+        <v>127.8779565</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1667282468132274</v>
+        <v>0.1776911733726564</v>
       </c>
       <c r="I19" t="n">
-        <v>-370.2225</v>
+        <v>-350.886</v>
       </c>
       <c r="J19" t="n">
-        <v>54.325</v>
+        <v>51.18175000000004</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8332717531867726</v>
+        <v>0.8223088266273436</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-102.92</v>
+        <v>-97.04500000000002</v>
       </c>
       <c r="G20" t="n">
-        <v>31.63127100000003</v>
+        <v>25.59708900000002</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-206.10375</v>
+        <v>-177.813</v>
       </c>
       <c r="J20" t="n">
-        <v>-63.14375000000002</v>
+        <v>-62.01474999999998</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -1670,25 +1670,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>192.11</v>
+        <v>155.3800000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>115.7836469999999</v>
+        <v>164.8428809999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7053389987068169</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="I21" t="n">
-        <v>-143.8325</v>
+        <v>-148.41225</v>
       </c>
       <c r="J21" t="n">
-        <v>283.2</v>
+        <v>283.62575</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7053389987068169</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1729,25 +1729,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>50.41</v>
+        <v>54.27000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>45.77527499999996</v>
+        <v>23.38060200000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7378468368479467</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="I22" t="n">
-        <v>-133.249</v>
+        <v>13.31899999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>89.99600000000002</v>
+        <v>84.059</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7378468368479467</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1788,25 +1788,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-236.265</v>
+        <v>61.20000000000002</v>
       </c>
       <c r="G23" t="n">
-        <v>148.2525869999999</v>
+        <v>51.07556999999998</v>
       </c>
       <c r="H23" t="n">
-        <v>0.272142064372919</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="I23" t="n">
-        <v>-356.202</v>
+        <v>-371.451</v>
       </c>
       <c r="J23" t="n">
-        <v>161.931</v>
+        <v>103.878</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.727857935627081</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1847,25 +1847,25 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-111.54</v>
+        <v>-89.66500000000002</v>
       </c>
       <c r="G24" t="n">
-        <v>22.73567100000001</v>
+        <v>53.82579300000009</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.1922349861858368</v>
       </c>
       <c r="I24" t="n">
-        <v>-132.46</v>
+        <v>-212.26</v>
       </c>
       <c r="J24" t="n">
-        <v>-63.01499999999999</v>
+        <v>89.24200000000005</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0.8077650138141632</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1906,25 +1906,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-109.1299999999999</v>
+        <v>-73.69</v>
       </c>
       <c r="G25" t="n">
-        <v>31.60161899999991</v>
+        <v>131.017362</v>
       </c>
       <c r="H25" t="n">
-        <v>0.01309655937846837</v>
+        <v>0.4561582085211575</v>
       </c>
       <c r="I25" t="n">
-        <v>-173.801</v>
+        <v>-161.743</v>
       </c>
       <c r="J25" t="n">
-        <v>-69.52499999999998</v>
+        <v>272.212</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9869034406215317</v>
+        <v>0.5438417914788425</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1965,25 +1965,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>59.28249999999998</v>
+        <v>64.69999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>48.51808499999999</v>
+        <v>41.66847299999994</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6025076990761109</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="I26" t="n">
-        <v>-138.32</v>
+        <v>-132.525</v>
       </c>
       <c r="J26" t="n">
-        <v>95.25375000000003</v>
+        <v>96.30799999999999</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6025076990761109</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2024,25 +2024,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>12.06499999999998</v>
+        <v>8.344999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>67.8326565</v>
+        <v>59.51156399999994</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6152661680598328</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="I27" t="n">
-        <v>-49.84125</v>
+        <v>-49.76300000000003</v>
       </c>
       <c r="J27" t="n">
-        <v>181.82</v>
+        <v>171.043</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6152661680598328</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2083,19 +2083,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-91.56000000000003</v>
+        <v>-93.96000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>34.05532199999998</v>
+        <v>32.12052899999998</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-134.275</v>
+        <v>-133.794</v>
       </c>
       <c r="J28" t="n">
-        <v>-54.97249999999999</v>
+        <v>-54.63499999999999</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -2142,25 +2142,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-126.0225</v>
+        <v>-123.655</v>
       </c>
       <c r="G29" t="n">
-        <v>44.68556400000002</v>
+        <v>45.67149300000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01319841619005719</v>
+        <v>0.01602136181575434</v>
       </c>
       <c r="I29" t="n">
-        <v>-181.8787500000001</v>
+        <v>-183.785</v>
       </c>
       <c r="J29" t="n">
-        <v>-68.37125000000002</v>
+        <v>-65.77200000000002</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9868015838099428</v>
+        <v>0.9839786381842457</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2201,25 +2201,25 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>59.68250000000002</v>
+        <v>50.25</v>
       </c>
       <c r="G30" t="n">
-        <v>21.79792650000001</v>
+        <v>45.29343000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9981099656357388</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="I30" t="n">
-        <v>19.38075</v>
+        <v>-141.49</v>
       </c>
       <c r="J30" t="n">
-        <v>84.98550000000003</v>
+        <v>88.93499999999999</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.9981099656357388</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>71.33749999999999</v>
+        <v>-166.58</v>
       </c>
       <c r="G31" t="n">
-        <v>35.78625749999996</v>
+        <v>245.985579</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8697594501718213</v>
+        <v>0.3662426088514603</v>
       </c>
       <c r="I31" t="n">
-        <v>-92.53775</v>
+        <v>-350.97</v>
       </c>
       <c r="J31" t="n">
-        <v>104.51025</v>
+        <v>177.515</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8697594501718213</v>
+        <v>0.6337573911485397</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-81.51000000000001</v>
+        <v>-108.48</v>
       </c>
       <c r="G32" t="n">
-        <v>44.50765200000001</v>
+        <v>27.45033900000002</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2271477663230241</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>-124.52575</v>
+        <v>-132.78</v>
       </c>
       <c r="J32" t="n">
-        <v>93.69275</v>
+        <v>-60.76500000000001</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.772852233676976</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2378,25 +2378,25 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-109.095</v>
+        <v>-114.2</v>
       </c>
       <c r="G33" t="n">
-        <v>56.53895099999998</v>
+        <v>34.80403499999995</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3108247422680412</v>
+        <v>0.009496506002508511</v>
       </c>
       <c r="I33" t="n">
-        <v>-164.56525</v>
+        <v>-173.255</v>
       </c>
       <c r="J33" t="n">
-        <v>269.6655</v>
+        <v>-70.75999999999999</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.6891752577319588</v>
+        <v>0.9905034939974915</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2437,25 +2437,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>54.215</v>
+        <v>23</v>
       </c>
       <c r="G34" t="n">
-        <v>53.36618700000005</v>
+        <v>34.80403499999999</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6021023125437982</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="I34" t="n">
-        <v>-139.443</v>
+        <v>-13.38700000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>93.39749999999999</v>
+        <v>70.47675000000002</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6021023125437982</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2496,25 +2496,25 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6.905000000000001</v>
+        <v>-91.96000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>106.37655</v>
+        <v>127.8779565</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5520672740014015</v>
+        <v>0.1776911733726564</v>
       </c>
       <c r="I35" t="n">
-        <v>-328.6905</v>
+        <v>-350.886</v>
       </c>
       <c r="J35" t="n">
-        <v>180.028</v>
+        <v>51.18175000000004</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5520672740014015</v>
+        <v>0.8223088266273436</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2555,19 +2555,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-99.03500000000003</v>
+        <v>-97.04500000000002</v>
       </c>
       <c r="G36" t="n">
-        <v>35.15244600000001</v>
+        <v>25.59708900000002</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>-134.0565</v>
+        <v>-177.813</v>
       </c>
       <c r="J36" t="n">
-        <v>-56.37199999999998</v>
+        <v>-62.01474999999998</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -2614,25 +2614,25 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-119.1849999999999</v>
+        <v>155.3800000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>43.50689699999995</v>
+        <v>164.8428809999999</v>
       </c>
       <c r="H37" t="n">
-        <v>0.008409250175192713</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="I37" t="n">
-        <v>-180.77</v>
+        <v>-148.41225</v>
       </c>
       <c r="J37" t="n">
-        <v>-68.79699999999998</v>
+        <v>283.62575</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9915907498248073</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2673,25 +2673,25 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>58.26499999999999</v>
+        <v>54.27000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>24.336879</v>
+        <v>23.38060200000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9793067770305225</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="I38" t="n">
-        <v>11.375</v>
+        <v>13.31899999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>86.16125000000001</v>
+        <v>84.059</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9793067770305225</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>53.23999999999999</v>
+        <v>61.20000000000002</v>
       </c>
       <c r="G39" t="n">
-        <v>63.8296365</v>
+        <v>51.07556999999998</v>
       </c>
       <c r="H39" t="n">
-        <v>0.665028453181583</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="I39" t="n">
-        <v>-338.22525</v>
+        <v>-371.451</v>
       </c>
       <c r="J39" t="n">
-        <v>103.51675</v>
+        <v>103.878</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.665028453181583</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2791,25 +2791,25 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-87.55750000000002</v>
+        <v>-89.66500000000002</v>
       </c>
       <c r="G40" t="n">
-        <v>37.54684500000003</v>
+        <v>53.82579300000009</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1709777547853078</v>
+        <v>0.1922349861858368</v>
       </c>
       <c r="I40" t="n">
-        <v>-126.84725</v>
+        <v>-212.26</v>
       </c>
       <c r="J40" t="n">
-        <v>84.91899999999987</v>
+        <v>89.24200000000005</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8290222452146923</v>
+        <v>0.8077650138141632</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-109.595</v>
+        <v>-73.69</v>
       </c>
       <c r="G41" t="n">
-        <v>44.98949700000004</v>
+        <v>131.017362</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2410760475944128</v>
+        <v>0.4561582085211575</v>
       </c>
       <c r="I41" t="n">
-        <v>-162.153</v>
+        <v>-161.743</v>
       </c>
       <c r="J41" t="n">
-        <v>267.0345</v>
+        <v>272.212</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7589239524055872</v>
+        <v>0.5438417914788425</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2909,25 +2909,25 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>12.02499999999998</v>
+        <v>64.69999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>22.32054300000005</v>
+        <v>41.66847299999994</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7464160560688117</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="I42" t="n">
-        <v>-17.33225000000001</v>
+        <v>-132.525</v>
       </c>
       <c r="J42" t="n">
-        <v>64.94099999999999</v>
+        <v>96.30799999999999</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.7464160560688117</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2968,25 +2968,25 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-72.28250000000001</v>
+        <v>8.344999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>103.0147545</v>
+        <v>59.51156399999994</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2021344377190188</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="I43" t="n">
-        <v>-299.162</v>
+        <v>-49.76300000000003</v>
       </c>
       <c r="J43" t="n">
-        <v>51.26849999999996</v>
+        <v>171.043</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7978655622809812</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3027,19 +3027,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-90.89500000000001</v>
+        <v>-93.96000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>17.84679750000008</v>
+        <v>32.12052899999998</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>-143.12575</v>
+        <v>-133.794</v>
       </c>
       <c r="J44" t="n">
-        <v>-58.83275000000001</v>
+        <v>-54.63499999999999</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -3086,25 +3086,25 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>8.845000000000027</v>
+        <v>-123.655</v>
       </c>
       <c r="G45" t="n">
-        <v>196.207284</v>
+        <v>45.67149300000001</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5140172029308697</v>
+        <v>0.01602136181575434</v>
       </c>
       <c r="I45" t="n">
-        <v>-161.87775</v>
+        <v>-183.785</v>
       </c>
       <c r="J45" t="n">
-        <v>277.98475</v>
+        <v>-65.77200000000002</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5140172029308697</v>
+        <v>0.9839786381842457</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -3145,25 +3145,25 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>49.42</v>
+        <v>50.25</v>
       </c>
       <c r="G46" t="n">
-        <v>21.089985</v>
+        <v>45.29343000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9646309314586995</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="I46" t="n">
-        <v>4.010499999999998</v>
+        <v>-141.49</v>
       </c>
       <c r="J46" t="n">
-        <v>74.21125000000001</v>
+        <v>88.93499999999999</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.9646309314586995</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -3204,25 +3204,25 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-182.8825</v>
+        <v>-166.58</v>
       </c>
       <c r="G47" t="n">
-        <v>196.281414</v>
+        <v>245.985579</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1186291739894552</v>
+        <v>0.3662426088514603</v>
       </c>
       <c r="I47" t="n">
-        <v>-392.76725</v>
+        <v>-350.97</v>
       </c>
       <c r="J47" t="n">
-        <v>59.9435</v>
+        <v>177.515</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.8813708260105448</v>
+        <v>0.6337573911485397</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -3263,19 +3263,19 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-142.2225</v>
+        <v>-108.48</v>
       </c>
       <c r="G48" t="n">
-        <v>51.891</v>
+        <v>27.45033900000002</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>-217.65675</v>
+        <v>-132.78</v>
       </c>
       <c r="J48" t="n">
-        <v>-82.58775000000001</v>
+        <v>-60.76500000000001</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -3322,25 +3322,25 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>232.665</v>
+        <v>-114.2</v>
       </c>
       <c r="G49" t="n">
-        <v>36.88338149999999</v>
+        <v>34.80403499999995</v>
       </c>
       <c r="H49" t="n">
-        <v>0.969463971880492</v>
+        <v>0.009496506002508511</v>
       </c>
       <c r="I49" t="n">
-        <v>55.3</v>
+        <v>-173.255</v>
       </c>
       <c r="J49" t="n">
-        <v>288.76175</v>
+        <v>-70.75999999999999</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.969463971880492</v>
+        <v>0.9905034939974915</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3381,25 +3381,25 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4892579999999997</v>
+        <v>0.3261720000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8338744588744589</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2449999999999999</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>1.575</v>
+        <v>1.07</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.8338744588744589</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.2</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6078660000000005</v>
+        <v>0.3409980000000003</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9315476190476191</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1549999999999999</v>
+        <v>-0.3717499999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>2.05125</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.9315476190476191</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-2.555</v>
+        <v>-1.2</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5040839999999998</v>
+        <v>0.185325</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>-3.31</v>
+        <v>-1.585</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.725</v>
+        <v>-0.78</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
@@ -3558,25 +3558,25 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.3</v>
+        <v>0.255</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4818449999999999</v>
+        <v>0.548562</v>
       </c>
       <c r="H53" t="n">
-        <v>0.7518939393939394</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.51</v>
+        <v>-0.765</v>
       </c>
       <c r="J53" t="n">
-        <v>1.135</v>
+        <v>1.105</v>
       </c>
       <c r="K53" t="b">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.7518939393939394</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -3617,25 +3617,25 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.54</v>
+        <v>0.4</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7857779999999996</v>
+        <v>0.6597570000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9994588744588745</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="I54" t="n">
-        <v>1.23</v>
+        <v>-0.5</v>
       </c>
       <c r="J54" t="n">
-        <v>3.93</v>
+        <v>2.561750000000002</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0.9994588744588745</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -3676,25 +3676,25 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-3.8</v>
+        <v>-1.145</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6375180000000008</v>
+        <v>0.4373669999999997</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.006951759005687803</v>
       </c>
       <c r="I55" t="n">
-        <v>-4.774999999999999</v>
+        <v>-3.095</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.5725</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K55" t="b">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0.9930482409943122</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.4750000000000002</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3261720000000003</v>
+        <v>0.4077149999999997</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9341400332532791</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.04374999999999996</v>
+        <v>-0.196</v>
       </c>
       <c r="J56" t="n">
-        <v>1.06</v>
+        <v>1.065</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0.9341400332532791</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -3794,25 +3794,25 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.3150000000000002</v>
+        <v>1.175</v>
       </c>
       <c r="G57" t="n">
-        <v>0.3558240000000006</v>
+        <v>0.8895600000000005</v>
       </c>
       <c r="H57" t="n">
-        <v>0.78865693700351</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.4300000000000002</v>
+        <v>-0.2399999999999998</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8750000000000001</v>
+        <v>2.325</v>
       </c>
       <c r="K57" t="b">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0.78865693700351</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -3853,25 +3853,25 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-1.205</v>
+        <v>-2.33</v>
       </c>
       <c r="G58" t="n">
-        <v>0.185325</v>
+        <v>1.008168</v>
       </c>
       <c r="H58" t="n">
-        <v>9.237021984112322e-05</v>
+        <v>0.0001454122437109205</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.59</v>
+        <v>-3.45</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.805</v>
+        <v>-1.08</v>
       </c>
       <c r="K58" t="b">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0.9999076297801589</v>
+        <v>0.9998545877562891</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -3912,25 +3912,25 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.2549999999999999</v>
+        <v>0.365</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5263230000000001</v>
+        <v>0.3261720000000003</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6615555145021245</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.745</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>1.07</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0.6615555145021245</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -3971,25 +3971,25 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.46</v>
+        <v>2.445</v>
       </c>
       <c r="G60" t="n">
-        <v>0.785778</v>
+        <v>0.7561259999999996</v>
       </c>
       <c r="H60" t="n">
-        <v>0.7888416774431923</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5037499999999999</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>2.58</v>
+        <v>3.464999999999999</v>
       </c>
       <c r="K60" t="b">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.7888416774431923</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -4030,25 +4030,25 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-1.225</v>
+        <v>-3.335</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6115725000000001</v>
+        <v>0.6523440000000006</v>
       </c>
       <c r="H61" t="n">
-        <v>0.006096434509514133</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>-3.235</v>
+        <v>-4.17</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-2.04</v>
       </c>
       <c r="K61" t="b">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.9939035654904859</v>
+        <v>1</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -4089,25 +4089,25 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.5249999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3632370000000001</v>
+        <v>0.4966710000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>0.9878905303947687</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="I62" t="n">
-        <v>0.13</v>
+        <v>-0.2439999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>2.620999999999999</v>
+        <v>1.698999999999999</v>
       </c>
       <c r="K62" t="b">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0.9878905303947687</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4148,25 +4148,25 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="G63" t="n">
-        <v>0.5930399999999998</v>
+        <v>0.6226919999999992</v>
       </c>
       <c r="H63" t="n">
-        <v>0.908694599176556</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4300000000000002</v>
+        <v>-0.2299999999999997</v>
       </c>
       <c r="J63" t="n">
-        <v>1.998</v>
+        <v>2.05</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0.908694599176556</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -4207,19 +4207,19 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>-2.365</v>
+        <v>-2.555</v>
       </c>
       <c r="G64" t="n">
-        <v>0.5114969999999996</v>
+        <v>0.5040839999999998</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>-3.23</v>
+        <v>-3.305</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.605</v>
+        <v>-1.735</v>
       </c>
       <c r="K64" t="b">
         <v>1</v>
@@ -4266,25 +4266,25 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.07000000000000006</v>
+        <v>0.2949999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2372159999999999</v>
+        <v>0.4892579999999997</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6139501089852264</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.455</v>
+        <v>-0.5950000000000002</v>
       </c>
       <c r="J65" t="n">
-        <v>0.4550000000000001</v>
+        <v>1.133999999999998</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0.6139501089852264</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -4325,25 +4325,25 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.955</v>
+        <v>2.545</v>
       </c>
       <c r="G66" t="n">
-        <v>0.7042350000000007</v>
+        <v>0.7783649999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="I66" t="n">
-        <v>1.65</v>
+        <v>1.235</v>
       </c>
       <c r="J66" t="n">
-        <v>3.977999999999999</v>
+        <v>3.925</v>
       </c>
       <c r="K66" t="b">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>-3.7</v>
+        <v>-3.785</v>
       </c>
       <c r="G67" t="n">
-        <v>0.7635390000000014</v>
+        <v>0.6449310000000007</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-4.735</v>
+        <v>-4.77</v>
       </c>
       <c r="J67" t="n">
-        <v>-2.357</v>
+        <v>-2.551000000000001</v>
       </c>
       <c r="K67" t="b">
         <v>1</v>
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.335</v>
+        <v>0.4</v>
       </c>
       <c r="G68" t="n">
-        <v>0.4003019999999999</v>
+        <v>0.3113460000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8516889015043997</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1849999999999998</v>
+        <v>0.004999999999999893</v>
       </c>
       <c r="J68" t="n">
-        <v>1.035</v>
+        <v>2.24</v>
       </c>
       <c r="K68" t="b">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0.8516889015043997</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4502,25 +4502,25 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.37</v>
+        <v>1.185</v>
       </c>
       <c r="G69" t="n">
-        <v>0.6375180000000008</v>
+        <v>0.5782140000000004</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9745955151859211</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2599999999999998</v>
+        <v>-0.165</v>
       </c>
       <c r="J69" t="n">
-        <v>2.36</v>
+        <v>2.135</v>
       </c>
       <c r="K69" t="b">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0.9745955151859211</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -4561,19 +4561,19 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>-2.545</v>
+        <v>-2.38</v>
       </c>
       <c r="G70" t="n">
-        <v>0.7264740000000003</v>
+        <v>0.5485620000000001</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>-3.48</v>
+        <v>-3.275</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.375</v>
+        <v>-1.58</v>
       </c>
       <c r="K70" t="b">
         <v>1</v>
@@ -4620,25 +4620,25 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.295</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="G71" t="n">
-        <v>0.355824</v>
+        <v>0.214977</v>
       </c>
       <c r="H71" t="n">
-        <v>0.7645472608572239</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2599999999999999</v>
+        <v>-0.38</v>
       </c>
       <c r="J71" t="n">
-        <v>0.82375</v>
+        <v>0.425</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0.7645472608572239</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -4679,25 +4679,25 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.725</v>
+        <v>3.024999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>0.659757000000001</v>
+        <v>0.6745830000000014</v>
       </c>
       <c r="H72" t="n">
-        <v>0.999858075503832</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>1.47</v>
+        <v>1.725</v>
       </c>
       <c r="J72" t="n">
-        <v>3.80375</v>
+        <v>4.175000000000001</v>
       </c>
       <c r="K72" t="b">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0.999858075503832</v>
+        <v>1</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -4738,19 +4738,19 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>-3.5</v>
+        <v>-3.655</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5633879999999998</v>
+        <v>0.7190610000000004</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>-4.253749999999999</v>
+        <v>-4.665</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.31</v>
+        <v>-2.42</v>
       </c>
       <c r="K73" t="b">
         <v>1</v>
@@ -4797,25 +4797,25 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.325</v>
+        <v>0.42</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4447799999999999</v>
+        <v>0.3261720000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>0.7958150523118461</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.285</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="K74" t="b">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0.7958150523118461</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -4856,25 +4856,25 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.245</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>0.6226919999999992</v>
+        <v>0.3409980000000003</v>
       </c>
       <c r="H75" t="n">
-        <v>0.9399257509281134</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1094999999999999</v>
+        <v>-0.3717499999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>2.095</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K75" t="b">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0.9399257509281134</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -4915,19 +4915,19 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>-2.6</v>
+        <v>-1.2</v>
       </c>
       <c r="G76" t="n">
-        <v>0.4966709999999999</v>
+        <v>0.185325</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>-3.335</v>
+        <v>-1.585</v>
       </c>
       <c r="J76" t="n">
-        <v>-1.75</v>
+        <v>-0.78</v>
       </c>
       <c r="K76" t="b">
         <v>1</v>
@@ -4974,25 +4974,25 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.4299999999999998</v>
+        <v>0.255</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4521929999999999</v>
+        <v>0.548562</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8147148160647992</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.41</v>
+        <v>-0.765</v>
       </c>
       <c r="J77" t="n">
-        <v>1.23</v>
+        <v>1.105</v>
       </c>
       <c r="K77" t="b">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0.8147148160647992</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -5033,25 +5033,25 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2.415</v>
+        <v>0.4</v>
       </c>
       <c r="G78" t="n">
-        <v>0.7042350000000001</v>
+        <v>0.6597570000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>0.9993250084373946</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="I78" t="n">
-        <v>1.1805</v>
+        <v>-0.5</v>
       </c>
       <c r="J78" t="n">
-        <v>3.634500000000001</v>
+        <v>2.561750000000002</v>
       </c>
       <c r="K78" t="b">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0.9993250084373946</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -5092,25 +5092,25 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>-3.8</v>
+        <v>-1.145</v>
       </c>
       <c r="G79" t="n">
-        <v>0.6004530000000003</v>
+        <v>0.4373669999999997</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.006951759005687803</v>
       </c>
       <c r="I79" t="n">
-        <v>-4.6995</v>
+        <v>-3.095</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.72</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K79" t="b">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0.9930482409943122</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -5151,25 +5151,25 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4750000000000002</v>
       </c>
       <c r="G80" t="n">
-        <v>0.4003019999999999</v>
+        <v>0.4077149999999997</v>
       </c>
       <c r="H80" t="n">
-        <v>0.9919284467713787</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="I80" t="n">
-        <v>0.16</v>
+        <v>-0.196</v>
       </c>
       <c r="J80" t="n">
-        <v>2.659249999999997</v>
+        <v>1.065</v>
       </c>
       <c r="K80" t="b">
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0.9919284467713787</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -5210,25 +5210,25 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.065</v>
+        <v>1.175</v>
       </c>
       <c r="G81" t="n">
-        <v>0.5930399999999998</v>
+        <v>0.8895600000000005</v>
       </c>
       <c r="H81" t="n">
-        <v>0.9013961605584643</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.46</v>
+        <v>-0.2399999999999998</v>
       </c>
       <c r="J81" t="n">
-        <v>1.92</v>
+        <v>2.325</v>
       </c>
       <c r="K81" t="b">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0.9013961605584643</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -5269,25 +5269,25 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>-2.365</v>
+        <v>-2.33</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4966709999999999</v>
+        <v>1.008168</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>0.0001454122437109205</v>
       </c>
       <c r="I82" t="n">
-        <v>-3.16925</v>
+        <v>-3.45</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.625</v>
+        <v>-1.08</v>
       </c>
       <c r="K82" t="b">
         <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0.9998545877562891</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -5328,25 +5328,25 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.05500000000000005</v>
+        <v>0.365</v>
       </c>
       <c r="G83" t="n">
-        <v>0.2372159999999999</v>
+        <v>0.3261720000000003</v>
       </c>
       <c r="H83" t="n">
-        <v>0.5842059336823735</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.515</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>0.3850000000000002</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="K83" t="b">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0.5842059336823735</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -5387,25 +5387,25 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2.98</v>
+        <v>2.445</v>
       </c>
       <c r="G84" t="n">
-        <v>0.726474</v>
+        <v>0.7561259999999996</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="I84" t="n">
-        <v>1.655</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>4.049999999999999</v>
+        <v>3.464999999999999</v>
       </c>
       <c r="K84" t="b">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -5446,19 +5446,19 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>-3.7</v>
+        <v>-3.335</v>
       </c>
       <c r="G85" t="n">
-        <v>0.800604</v>
+        <v>0.6523440000000006</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>-4.785000000000001</v>
+        <v>-4.17</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.285750000000003</v>
+        <v>-2.04</v>
       </c>
       <c r="K85" t="b">
         <v>1</v>
@@ -5505,25 +5505,25 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.3300000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="G86" t="n">
-        <v>0.392889</v>
+        <v>0.4966710000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>0.853518821603928</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.18</v>
+        <v>-0.2439999999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>1.027249999999999</v>
+        <v>1.698999999999999</v>
       </c>
       <c r="K86" t="b">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0.853518821603928</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -5564,25 +5564,25 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1.365</v>
+        <v>1.19</v>
       </c>
       <c r="G87" t="n">
-        <v>0.6375180000000003</v>
+        <v>0.6226919999999992</v>
       </c>
       <c r="H87" t="n">
-        <v>0.9755864702673214</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2677500000000001</v>
+        <v>-0.2299999999999997</v>
       </c>
       <c r="J87" t="n">
-        <v>2.357249999999999</v>
+        <v>2.05</v>
       </c>
       <c r="K87" t="b">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0.9755864702673214</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -5623,19 +5623,19 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>-2.54</v>
+        <v>-2.555</v>
       </c>
       <c r="G88" t="n">
-        <v>0.7264740000000003</v>
+        <v>0.5040839999999998</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>-3.475</v>
+        <v>-3.305</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.377750000000001</v>
+        <v>-1.735</v>
       </c>
       <c r="K88" t="b">
         <v>1</v>
@@ -5682,25 +5682,25 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.295</v>
+        <v>0.2949999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>0.3558240000000001</v>
+        <v>0.4892579999999997</v>
       </c>
       <c r="H89" t="n">
-        <v>0.7652755046372067</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.255</v>
+        <v>-0.5950000000000002</v>
       </c>
       <c r="J89" t="n">
-        <v>0.8250000000000001</v>
+        <v>1.133999999999998</v>
       </c>
       <c r="K89" t="b">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0.7652755046372067</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -5741,25 +5741,25 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.745</v>
+        <v>2.545</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6523440000000006</v>
+        <v>0.7783649999999999</v>
       </c>
       <c r="H90" t="n">
-        <v>0.9998636115657392</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="I90" t="n">
-        <v>1.485</v>
+        <v>1.235</v>
       </c>
       <c r="J90" t="n">
-        <v>3.795</v>
+        <v>3.925</v>
       </c>
       <c r="K90" t="b">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0.9998636115657392</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -5800,19 +5800,19 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>-3.52</v>
+        <v>-3.785</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5633880000000004</v>
+        <v>0.6449310000000007</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>-4.289999999999999</v>
+        <v>-4.77</v>
       </c>
       <c r="J91" t="n">
-        <v>-2.32</v>
+        <v>-2.551000000000001</v>
       </c>
       <c r="K91" t="b">
         <v>1</v>
@@ -5859,25 +5859,25 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G92" t="n">
-        <v>0.3261720000000001</v>
+        <v>0.3113460000000001</v>
       </c>
       <c r="H92" t="n">
-        <v>0.9347383989646885</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.04000000000000004</v>
+        <v>0.004999999999999893</v>
       </c>
       <c r="J92" t="n">
-        <v>1.06</v>
+        <v>2.24</v>
       </c>
       <c r="K92" t="b">
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0.9347383989646885</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -5918,25 +5918,25 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0.3150000000000002</v>
+        <v>1.185</v>
       </c>
       <c r="G93" t="n">
-        <v>0.3558240000000006</v>
+        <v>0.5782140000000004</v>
       </c>
       <c r="H93" t="n">
-        <v>0.7885006470696987</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.4300000000000002</v>
+        <v>-0.165</v>
       </c>
       <c r="J93" t="n">
-        <v>0.8750000000000001</v>
+        <v>2.135</v>
       </c>
       <c r="K93" t="b">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0.7885006470696987</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -5977,25 +5977,25 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>-1.205</v>
+        <v>-2.38</v>
       </c>
       <c r="G94" t="n">
-        <v>0.185325</v>
+        <v>0.5485620000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>9.243852837862822e-05</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.59</v>
+        <v>-3.275</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.805</v>
+        <v>-1.58</v>
       </c>
       <c r="K94" t="b">
         <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>0.9999075614716214</v>
+        <v>1</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -6036,25 +6036,25 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0.2549999999999999</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="G95" t="n">
-        <v>0.526323</v>
+        <v>0.214977</v>
       </c>
       <c r="H95" t="n">
-        <v>0.661859863190978</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.745</v>
+        <v>-0.38</v>
       </c>
       <c r="J95" t="n">
-        <v>1.07</v>
+        <v>0.425</v>
       </c>
       <c r="K95" t="b">
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0.661859863190978</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -6095,25 +6095,25 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.46</v>
+        <v>3.024999999999999</v>
       </c>
       <c r="G96" t="n">
-        <v>0.7857779999999999</v>
+        <v>0.6745830000000014</v>
       </c>
       <c r="H96" t="n">
-        <v>0.7886855241264559</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5049999999999999</v>
+        <v>1.725</v>
       </c>
       <c r="J96" t="n">
-        <v>2.58</v>
+        <v>4.175000000000001</v>
       </c>
       <c r="K96" t="b">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0.7886855241264559</v>
+        <v>1</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -6154,25 +6154,25 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>-1.225</v>
+        <v>-3.655</v>
       </c>
       <c r="G97" t="n">
-        <v>0.6078660000000001</v>
+        <v>0.7190610000000004</v>
       </c>
       <c r="H97" t="n">
-        <v>0.006100942872989462</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>-3.23575</v>
+        <v>-4.665</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-2.42</v>
       </c>
       <c r="K97" t="b">
         <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>0.9938990571270105</v>
+        <v>1</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -6213,25 +6213,25 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.4400000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3335850000000001</v>
+        <v>0.3261720000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9383824122630092</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.02999999999999993</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>1.075</v>
+        <v>1.07</v>
       </c>
       <c r="K98" t="b">
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0.9383824122630092</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0.3350000000000002</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="G99" t="n">
-        <v>0.3484109999999998</v>
+        <v>0.3409980000000003</v>
       </c>
       <c r="H99" t="n">
-        <v>0.8125252117789431</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3600000000000001</v>
+        <v>-0.3717499999999999</v>
       </c>
       <c r="J99" t="n">
-        <v>0.8899999999999999</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K99" t="b">
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0.8125252117789431</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -6337,19 +6337,19 @@
         <v>0.185325</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0001008471157724889</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>-1.58</v>
+        <v>-1.585</v>
       </c>
       <c r="J100" t="n">
-        <v>-0.80375</v>
+        <v>-0.78</v>
       </c>
       <c r="K100" t="b">
         <v>1</v>
       </c>
       <c r="L100" t="n">
-        <v>0.9998991528842275</v>
+        <v>1</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -6390,25 +6390,25 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.24</v>
+        <v>0.255</v>
       </c>
       <c r="G101" t="n">
-        <v>0.526323</v>
+        <v>0.548562</v>
       </c>
       <c r="H101" t="n">
-        <v>0.6558087938684953</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.72</v>
+        <v>-0.765</v>
       </c>
       <c r="J101" t="n">
-        <v>1.075</v>
+        <v>1.105</v>
       </c>
       <c r="K101" t="b">
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0.6558087938684953</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -6449,25 +6449,25 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0.4450000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="G102" t="n">
-        <v>0.7487130000000002</v>
+        <v>0.6597570000000001</v>
       </c>
       <c r="H102" t="n">
-        <v>0.7934651068979427</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.4550000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="J102" t="n">
-        <v>2.62125</v>
+        <v>2.561750000000002</v>
       </c>
       <c r="K102" t="b">
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>0.7934651068979427</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -6508,25 +6508,25 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>-1.17</v>
+        <v>-1.145</v>
       </c>
       <c r="G103" t="n">
-        <v>0.4892580000000001</v>
+        <v>0.4373669999999997</v>
       </c>
       <c r="H103" t="n">
-        <v>0.006655909640984268</v>
+        <v>0.006951759005687803</v>
       </c>
       <c r="I103" t="n">
-        <v>-3.25</v>
+        <v>-3.095</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.58</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K103" t="b">
         <v>1</v>
       </c>
       <c r="L103" t="n">
-        <v>0.9933440903590157</v>
+        <v>0.9930482409943122</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -6567,25 +6567,25 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0.425</v>
+        <v>0.4750000000000002</v>
       </c>
       <c r="G104" t="n">
-        <v>0.2816940000000001</v>
+        <v>0.4077149999999997</v>
       </c>
       <c r="H104" t="n">
-        <v>0.8883349950149552</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2200000000000001</v>
+        <v>-0.196</v>
       </c>
       <c r="J104" t="n">
-        <v>0.9945000000000001</v>
+        <v>1.065</v>
       </c>
       <c r="K104" t="b">
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0.8883349950149552</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -6626,25 +6626,25 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0.05500000000000016</v>
+        <v>1.175</v>
       </c>
       <c r="G105" t="n">
-        <v>0.4225410000000002</v>
+        <v>0.8895600000000005</v>
       </c>
       <c r="H105" t="n">
-        <v>0.551345962113659</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.8390000000000003</v>
+        <v>-0.2399999999999998</v>
       </c>
       <c r="J105" t="n">
-        <v>0.8379999999999999</v>
+        <v>2.325</v>
       </c>
       <c r="K105" t="b">
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0.551345962113659</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -6685,25 +6685,25 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>-1.275</v>
+        <v>-2.33</v>
       </c>
       <c r="G106" t="n">
-        <v>0.2149770000000003</v>
+        <v>1.008168</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>0.0001454122437109205</v>
       </c>
       <c r="I106" t="n">
-        <v>-2.764</v>
+        <v>-3.45</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.9155000000000002</v>
+        <v>-1.08</v>
       </c>
       <c r="K106" t="b">
         <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>1</v>
+        <v>0.9998545877562891</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -6744,25 +6744,25 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0.335</v>
+        <v>0.365</v>
       </c>
       <c r="G107" t="n">
-        <v>0.4966709999999999</v>
+        <v>0.3261720000000003</v>
       </c>
       <c r="H107" t="n">
-        <v>0.6989032901296112</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="I107" t="n">
-        <v>-1.13</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>1.01</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="K107" t="b">
         <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>0.6989032901296112</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -6803,25 +6803,25 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.7550000000000003</v>
+        <v>2.445</v>
       </c>
       <c r="G108" t="n">
-        <v>1.060059</v>
+        <v>0.7561259999999996</v>
       </c>
       <c r="H108" t="n">
-        <v>0.7617148554336989</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.8100000000000005</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>2.329</v>
+        <v>3.464999999999999</v>
       </c>
       <c r="K108" t="b">
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>0.7617148554336989</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -6862,19 +6862,19 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>-2.205</v>
+        <v>-3.335</v>
       </c>
       <c r="G109" t="n">
-        <v>0.3409979999999993</v>
+        <v>0.6523440000000006</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>-3.3095</v>
+        <v>-4.17</v>
       </c>
       <c r="J109" t="n">
-        <v>-1.4755</v>
+        <v>-2.04</v>
       </c>
       <c r="K109" t="b">
         <v>1</v>
@@ -6921,25 +6921,25 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0.4750000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="G110" t="n">
-        <v>0.4670190000000001</v>
+        <v>0.4966710000000001</v>
       </c>
       <c r="H110" t="n">
-        <v>0.8812750524909334</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.18</v>
+        <v>-0.2439999999999999</v>
       </c>
       <c r="J110" t="n">
-        <v>1.925</v>
+        <v>1.698999999999999</v>
       </c>
       <c r="K110" t="b">
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0.8812750524909334</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -6980,25 +6980,25 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="G111" t="n">
-        <v>0.5930399999999998</v>
+        <v>0.6226919999999992</v>
       </c>
       <c r="H111" t="n">
-        <v>0.91849589616339</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2849999999999997</v>
+        <v>-0.2299999999999997</v>
       </c>
       <c r="J111" t="n">
-        <v>1.995</v>
+        <v>2.05</v>
       </c>
       <c r="K111" t="b">
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>0.91849589616339</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -7039,19 +7039,19 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>-2.48</v>
+        <v>-2.555</v>
       </c>
       <c r="G112" t="n">
-        <v>0.4966710000000006</v>
+        <v>0.5040839999999998</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>-3.2705</v>
+        <v>-3.305</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.709500000000003</v>
+        <v>-1.735</v>
       </c>
       <c r="K112" t="b">
         <v>1</v>
@@ -7098,25 +7098,25 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0.175</v>
+        <v>0.2949999999999999</v>
       </c>
       <c r="G113" t="n">
-        <v>0.415128</v>
+        <v>0.4892579999999997</v>
       </c>
       <c r="H113" t="n">
-        <v>0.6995609849207864</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5399999999999999</v>
+        <v>-0.5950000000000002</v>
       </c>
       <c r="J113" t="n">
-        <v>1.03</v>
+        <v>1.133999999999998</v>
       </c>
       <c r="K113" t="b">
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>0.6995609849207864</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -7157,25 +7157,25 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2.685</v>
+        <v>2.545</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8302559999999987</v>
+        <v>0.7783649999999999</v>
       </c>
       <c r="H114" t="n">
-        <v>0.9996182477572055</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="I114" t="n">
-        <v>1.345</v>
+        <v>1.235</v>
       </c>
       <c r="J114" t="n">
-        <v>4.02</v>
+        <v>3.925</v>
       </c>
       <c r="K114" t="b">
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>0.9996182477572055</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -7216,19 +7216,19 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>-3.79</v>
+        <v>-3.785</v>
       </c>
       <c r="G115" t="n">
-        <v>0.6894090000000004</v>
+        <v>0.6449310000000007</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>-4.795000000000001</v>
+        <v>-4.77</v>
       </c>
       <c r="J115" t="n">
-        <v>-2.46</v>
+        <v>-2.551000000000001</v>
       </c>
       <c r="K115" t="b">
         <v>1</v>
@@ -7275,25 +7275,25 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0.3800000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="G116" t="n">
-        <v>0.3780630000000003</v>
+        <v>0.3113460000000001</v>
       </c>
       <c r="H116" t="n">
-        <v>0.8870950833420694</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.135</v>
+        <v>0.004999999999999893</v>
       </c>
       <c r="J116" t="n">
-        <v>1.29</v>
+        <v>2.24</v>
       </c>
       <c r="K116" t="b">
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>0.8870950833420694</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -7334,25 +7334,25 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1.315</v>
+        <v>1.185</v>
       </c>
       <c r="G117" t="n">
-        <v>0.6301050000000004</v>
+        <v>0.5782140000000004</v>
       </c>
       <c r="H117" t="n">
-        <v>0.9621553621972954</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1250000000000002</v>
+        <v>-0.165</v>
       </c>
       <c r="J117" t="n">
-        <v>2.32</v>
+        <v>2.135</v>
       </c>
       <c r="K117" t="b">
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>0.9621553621972954</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -7393,19 +7393,19 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>-2.485</v>
+        <v>-2.38</v>
       </c>
       <c r="G118" t="n">
-        <v>0.6894090000000004</v>
+        <v>0.5485620000000001</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>-3.445</v>
+        <v>-3.275</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.42</v>
+        <v>-1.58</v>
       </c>
       <c r="K118" t="b">
         <v>1</v>
@@ -7452,25 +7452,25 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0.2100000000000001</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="G119" t="n">
-        <v>0.355824</v>
+        <v>0.214977</v>
       </c>
       <c r="H119" t="n">
-        <v>0.7332005451305168</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2949999999999999</v>
+        <v>-0.38</v>
       </c>
       <c r="J119" t="n">
-        <v>0.79</v>
+        <v>0.425</v>
       </c>
       <c r="K119" t="b">
         <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>0.7332005451305168</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -7511,19 +7511,19 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>2.785</v>
+        <v>3.024999999999999</v>
       </c>
       <c r="G120" t="n">
-        <v>0.6745829999999987</v>
+        <v>0.6745830000000014</v>
       </c>
       <c r="H120" t="n">
         <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>1.725</v>
       </c>
       <c r="J120" t="n">
-        <v>3.840500000000002</v>
+        <v>4.175000000000001</v>
       </c>
       <c r="K120" t="b">
         <v>0</v>
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>-3.54</v>
+        <v>-3.655</v>
       </c>
       <c r="G121" t="n">
-        <v>0.6004530000000003</v>
+        <v>0.7190610000000004</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>-4.425</v>
+        <v>-4.665</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.325</v>
+        <v>-2.42</v>
       </c>
       <c r="K121" t="b">
         <v>1</v>
@@ -7629,25 +7629,25 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3261720000000003</v>
+        <v>0.3261720000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>0.9341400332532791</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.04374999999999996</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="K122" t="b">
         <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>0.9341400332532791</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -7688,25 +7688,25 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0.3150000000000002</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="G123" t="n">
-        <v>0.3558240000000006</v>
+        <v>0.3409980000000003</v>
       </c>
       <c r="H123" t="n">
-        <v>0.78865693700351</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.4300000000000002</v>
+        <v>-0.3717499999999999</v>
       </c>
       <c r="J123" t="n">
-        <v>0.8750000000000001</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K123" t="b">
         <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>0.78865693700351</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -7747,25 +7747,25 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>-1.205</v>
+        <v>-1.2</v>
       </c>
       <c r="G124" t="n">
         <v>0.185325</v>
       </c>
       <c r="H124" t="n">
-        <v>9.237021984112322e-05</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>-1.59</v>
+        <v>-1.585</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.805</v>
+        <v>-0.78</v>
       </c>
       <c r="K124" t="b">
         <v>1</v>
       </c>
       <c r="L124" t="n">
-        <v>0.9999076297801589</v>
+        <v>1</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
@@ -7806,25 +7806,25 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0.2549999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="G125" t="n">
-        <v>0.5263230000000001</v>
+        <v>0.548562</v>
       </c>
       <c r="H125" t="n">
-        <v>0.6615555145021245</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.745</v>
+        <v>-0.765</v>
       </c>
       <c r="J125" t="n">
-        <v>1.07</v>
+        <v>1.105</v>
       </c>
       <c r="K125" t="b">
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>0.6615555145021245</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -7865,25 +7865,25 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="G126" t="n">
-        <v>0.785778</v>
+        <v>0.6597570000000001</v>
       </c>
       <c r="H126" t="n">
-        <v>0.7888416774431923</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5037499999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="J126" t="n">
-        <v>2.58</v>
+        <v>2.561750000000002</v>
       </c>
       <c r="K126" t="b">
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>0.7888416774431923</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -7924,25 +7924,25 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>-1.225</v>
+        <v>-1.145</v>
       </c>
       <c r="G127" t="n">
-        <v>0.6115725000000001</v>
+        <v>0.4373669999999997</v>
       </c>
       <c r="H127" t="n">
-        <v>0.006096434509514133</v>
+        <v>0.006951759005687803</v>
       </c>
       <c r="I127" t="n">
-        <v>-3.235</v>
+        <v>-3.095</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K127" t="b">
         <v>1</v>
       </c>
       <c r="L127" t="n">
-        <v>0.9939035654904859</v>
+        <v>0.9930482409943122</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -7983,25 +7983,25 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>0.53</v>
+        <v>0.4750000000000002</v>
       </c>
       <c r="G128" t="n">
-        <v>0.363237</v>
+        <v>0.4077149999999997</v>
       </c>
       <c r="H128" t="n">
-        <v>0.9895522388059701</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="I128" t="n">
-        <v>0.145</v>
+        <v>-0.196</v>
       </c>
       <c r="J128" t="n">
-        <v>2.645249999999999</v>
+        <v>1.065</v>
       </c>
       <c r="K128" t="b">
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>0.9895522388059701</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -8042,25 +8042,25 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1.09</v>
+        <v>1.175</v>
       </c>
       <c r="G129" t="n">
-        <v>0.600453</v>
+        <v>0.8895600000000005</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9062189054726368</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.2399999999999998</v>
       </c>
       <c r="J129" t="n">
-        <v>1.985</v>
+        <v>2.325</v>
       </c>
       <c r="K129" t="b">
         <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>0.9062189054726368</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -8101,25 +8101,25 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>-2.38</v>
+        <v>-2.33</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5040839999999998</v>
+        <v>1.008168</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>0.0001454122437109205</v>
       </c>
       <c r="I130" t="n">
-        <v>-3.22</v>
+        <v>-3.45</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.62</v>
+        <v>-1.08</v>
       </c>
       <c r="K130" t="b">
         <v>1</v>
       </c>
       <c r="L130" t="n">
-        <v>1</v>
+        <v>0.9998545877562891</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -8160,25 +8160,25 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>0.06499999999999995</v>
+        <v>0.365</v>
       </c>
       <c r="G131" t="n">
-        <v>0.2372159999999999</v>
+        <v>0.3261720000000003</v>
       </c>
       <c r="H131" t="n">
-        <v>0.6044776119402985</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4750000000000001</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="J131" t="n">
-        <v>0.4199999999999999</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="K131" t="b">
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>0.6044776119402985</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -8219,25 +8219,25 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2.975000000000001</v>
+        <v>2.445</v>
       </c>
       <c r="G132" t="n">
-        <v>0.7042350000000007</v>
+        <v>0.7561259999999996</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="I132" t="n">
-        <v>1.655</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>3.99</v>
+        <v>3.464999999999999</v>
       </c>
       <c r="K132" t="b">
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>1</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>-3.71</v>
+        <v>-3.335</v>
       </c>
       <c r="G133" t="n">
-        <v>0.7709520000000013</v>
+        <v>0.6523440000000006</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>-4.74</v>
+        <v>-4.17</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.329750000000002</v>
+        <v>-2.04</v>
       </c>
       <c r="K133" t="b">
         <v>1</v>
@@ -8337,25 +8337,25 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="G134" t="n">
-        <v>0.4818450000000002</v>
+        <v>0.4966710000000001</v>
       </c>
       <c r="H134" t="n">
-        <v>0.8329706202393906</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.245</v>
+        <v>-0.2439999999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>1.575</v>
+        <v>1.698999999999999</v>
       </c>
       <c r="K134" t="b">
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0.8329706202393906</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -8396,25 +8396,25 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="G135" t="n">
-        <v>0.6078659999999998</v>
+        <v>0.6226919999999992</v>
       </c>
       <c r="H135" t="n">
-        <v>0.9311751904243744</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1562499999999999</v>
+        <v>-0.2299999999999997</v>
       </c>
       <c r="J135" t="n">
-        <v>2.055</v>
+        <v>2.05</v>
       </c>
       <c r="K135" t="b">
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0.9311751904243744</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -8458,16 +8458,16 @@
         <v>-2.555</v>
       </c>
       <c r="G136" t="n">
-        <v>0.5040840000000004</v>
+        <v>0.5040839999999998</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>-3.31</v>
+        <v>-3.305</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.725</v>
+        <v>-1.735</v>
       </c>
       <c r="K136" t="b">
         <v>1</v>
@@ -8514,25 +8514,25 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0.3049999999999999</v>
+        <v>0.2949999999999999</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4744320000000001</v>
+        <v>0.4892579999999997</v>
       </c>
       <c r="H137" t="n">
-        <v>0.7559847660500544</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.48125</v>
+        <v>-0.5950000000000002</v>
       </c>
       <c r="J137" t="n">
-        <v>1.13625</v>
+        <v>1.133999999999998</v>
       </c>
       <c r="K137" t="b">
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>0.7559847660500544</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -8573,25 +8573,25 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>2.53</v>
+        <v>2.545</v>
       </c>
       <c r="G138" t="n">
-        <v>0.7709520000000006</v>
+        <v>0.7783649999999999</v>
       </c>
       <c r="H138" t="n">
-        <v>0.999455930359086</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="I138" t="n">
-        <v>1.22875</v>
+        <v>1.235</v>
       </c>
       <c r="J138" t="n">
-        <v>3.8825</v>
+        <v>3.925</v>
       </c>
       <c r="K138" t="b">
         <v>0</v>
       </c>
       <c r="L138" t="n">
-        <v>0.999455930359086</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -8632,19 +8632,19 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>-3.805</v>
+        <v>-3.785</v>
       </c>
       <c r="G139" t="n">
-        <v>0.6375179999999996</v>
+        <v>0.6449310000000007</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>-4.774999999999999</v>
+        <v>-4.77</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.645</v>
+        <v>-2.551000000000001</v>
       </c>
       <c r="K139" t="b">
         <v>1</v>
@@ -8691,25 +8691,25 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="G140" t="n">
-        <v>0.3928890000000002</v>
+        <v>0.3113460000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>0.8532404181184668</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.18</v>
+        <v>0.004999999999999893</v>
       </c>
       <c r="J140" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="K140" t="b">
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>0.8532404181184668</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -8750,25 +8750,25 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1.36</v>
+        <v>1.185</v>
       </c>
       <c r="G141" t="n">
-        <v>0.6375180000000003</v>
+        <v>0.5782140000000004</v>
       </c>
       <c r="H141" t="n">
-        <v>0.9750522648083624</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2649999999999999</v>
+        <v>-0.165</v>
       </c>
       <c r="J141" t="n">
-        <v>2.36</v>
+        <v>2.135</v>
       </c>
       <c r="K141" t="b">
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0.9750522648083624</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -8809,19 +8809,19 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>-2.53</v>
+        <v>-2.38</v>
       </c>
       <c r="G142" t="n">
-        <v>0.7338870000000001</v>
+        <v>0.5485620000000001</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>-3.475</v>
+        <v>-3.275</v>
       </c>
       <c r="J142" t="n">
-        <v>-1.375</v>
+        <v>-1.58</v>
       </c>
       <c r="K142" t="b">
         <v>1</v>
@@ -8868,25 +8868,25 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0.2999999999999999</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="G143" t="n">
-        <v>0.355824</v>
+        <v>0.214977</v>
       </c>
       <c r="H143" t="n">
-        <v>0.7654355400696864</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2550000000000002</v>
+        <v>-0.38</v>
       </c>
       <c r="J143" t="n">
-        <v>0.8299999999999998</v>
+        <v>0.425</v>
       </c>
       <c r="K143" t="b">
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>0.7654355400696864</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -8927,25 +8927,25 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>2.725</v>
+        <v>3.024999999999999</v>
       </c>
       <c r="G144" t="n">
-        <v>0.6597569999999997</v>
+        <v>0.6745830000000014</v>
       </c>
       <c r="H144" t="n">
-        <v>0.9998606271777003</v>
+        <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>1.475</v>
+        <v>1.725</v>
       </c>
       <c r="J144" t="n">
-        <v>3.815</v>
+        <v>4.175000000000001</v>
       </c>
       <c r="K144" t="b">
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>0.9998606271777003</v>
+        <v>1</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -8986,19 +8986,19 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>-3.495</v>
+        <v>-3.655</v>
       </c>
       <c r="G145" t="n">
-        <v>0.5633879999999998</v>
+        <v>0.7190610000000004</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>-4.26</v>
+        <v>-4.665</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.308500000000004</v>
+        <v>-2.42</v>
       </c>
       <c r="K145" t="b">
         <v>1</v>
@@ -9045,25 +9045,25 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>51.44</v>
+        <v>23</v>
       </c>
       <c r="G146" t="n">
-        <v>58.08826800000001</v>
+        <v>34.80403499999999</v>
       </c>
       <c r="H146" t="n">
-        <v>0.5888162672476398</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="I146" t="n">
-        <v>-138.325</v>
+        <v>-13.38700000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>93.40999999999998</v>
+        <v>70.47675000000002</v>
       </c>
       <c r="K146" t="b">
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>0.5888162672476398</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -9104,25 +9104,25 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>7.525000000000006</v>
+        <v>-91.96000000000001</v>
       </c>
       <c r="G147" t="n">
-        <v>94.31559899999996</v>
+        <v>127.8779565</v>
       </c>
       <c r="H147" t="n">
-        <v>0.5604938271604938</v>
+        <v>0.1776911733726564</v>
       </c>
       <c r="I147" t="n">
-        <v>-317.1369999999999</v>
+        <v>-350.886</v>
       </c>
       <c r="J147" t="n">
-        <v>178.927</v>
+        <v>51.18175000000004</v>
       </c>
       <c r="K147" t="b">
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0.5604938271604938</v>
+        <v>0.8223088266273436</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -9163,19 +9163,19 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>-99.375</v>
+        <v>-97.04500000000002</v>
       </c>
       <c r="G148" t="n">
-        <v>35.90857199999996</v>
+        <v>25.59708900000002</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>-134.064</v>
+        <v>-177.813</v>
       </c>
       <c r="J148" t="n">
-        <v>-56.23099999999999</v>
+        <v>-62.01474999999998</v>
       </c>
       <c r="K148" t="b">
         <v>0</v>
@@ -9222,25 +9222,25 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>-118.24</v>
+        <v>155.3800000000001</v>
       </c>
       <c r="G149" t="n">
-        <v>44.41869600000005</v>
+        <v>164.8428809999999</v>
       </c>
       <c r="H149" t="n">
-        <v>0.008714596949891068</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="I149" t="n">
-        <v>-180.879</v>
+        <v>-148.41225</v>
       </c>
       <c r="J149" t="n">
-        <v>-68.65100000000002</v>
+        <v>283.62575</v>
       </c>
       <c r="K149" t="b">
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>0.9912854030501089</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -9281,25 +9281,25 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>9.344999999999999</v>
+        <v>54.27000000000001</v>
       </c>
       <c r="G150" t="n">
-        <v>18.762303</v>
+        <v>23.38060200000001</v>
       </c>
       <c r="H150" t="n">
-        <v>0.7068258777401533</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="I150" t="n">
-        <v>-19.13999999999999</v>
+        <v>13.31899999999999</v>
       </c>
       <c r="J150" t="n">
-        <v>58.36250000000001</v>
+        <v>84.059</v>
       </c>
       <c r="K150" t="b">
         <v>0</v>
       </c>
       <c r="L150" t="n">
-        <v>0.7068258777401533</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
@@ -9340,25 +9340,25 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>-80.49000000000001</v>
+        <v>61.20000000000002</v>
       </c>
       <c r="G151" t="n">
-        <v>114.745827</v>
+        <v>51.07556999999998</v>
       </c>
       <c r="H151" t="n">
-        <v>0.2040634468009268</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="I151" t="n">
-        <v>-307.9425</v>
+        <v>-371.451</v>
       </c>
       <c r="J151" t="n">
-        <v>54.21250000000001</v>
+        <v>103.878</v>
       </c>
       <c r="K151" t="b">
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>0.7959365531990732</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -9399,25 +9399,25 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>-92.67999999999998</v>
+        <v>-89.66500000000002</v>
       </c>
       <c r="G152" t="n">
-        <v>21.53476499999996</v>
+        <v>53.82579300000009</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>0.1922349861858368</v>
       </c>
       <c r="I152" t="n">
-        <v>-172.2025</v>
+        <v>-212.26</v>
       </c>
       <c r="J152" t="n">
-        <v>-59.41999999999999</v>
+        <v>89.24200000000005</v>
       </c>
       <c r="K152" t="b">
         <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
+        <v>0.8077650138141632</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -9458,25 +9458,25 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>-35.26499999999999</v>
+        <v>-73.69</v>
       </c>
       <c r="G153" t="n">
-        <v>135.502227</v>
+        <v>131.017362</v>
       </c>
       <c r="H153" t="n">
-        <v>0.4336125467831046</v>
+        <v>0.4561582085211575</v>
       </c>
       <c r="I153" t="n">
-        <v>-163.395</v>
+        <v>-161.743</v>
       </c>
       <c r="J153" t="n">
-        <v>223.0725</v>
+        <v>272.212</v>
       </c>
       <c r="K153" t="b">
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>0.5663874532168953</v>
+        <v>0.5438417914788425</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -9517,25 +9517,25 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>50.80250000000001</v>
+        <v>64.69999999999999</v>
       </c>
       <c r="G154" t="n">
-        <v>21.41986349999998</v>
+        <v>41.66847299999994</v>
       </c>
       <c r="H154" t="n">
-        <v>0.9824345146379044</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="I154" t="n">
-        <v>8.498499999999995</v>
+        <v>-132.525</v>
       </c>
       <c r="J154" t="n">
-        <v>75.93324999999999</v>
+        <v>96.30799999999999</v>
       </c>
       <c r="K154" t="b">
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>0.9824345146379044</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -9576,25 +9576,25 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>-103.805</v>
+        <v>8.344999999999999</v>
       </c>
       <c r="G155" t="n">
-        <v>184.6986015</v>
+        <v>59.51156399999994</v>
       </c>
       <c r="H155" t="n">
-        <v>0.2406779661016949</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="I155" t="n">
-        <v>-386.6075</v>
+        <v>-49.76300000000003</v>
       </c>
       <c r="J155" t="n">
-        <v>94.26699999999997</v>
+        <v>171.043</v>
       </c>
       <c r="K155" t="b">
         <v>0</v>
       </c>
       <c r="L155" t="n">
-        <v>0.7593220338983051</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -9635,25 +9635,25 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>-114.1875</v>
+        <v>-93.96000000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>49.24455900000009</v>
+        <v>32.12052899999998</v>
       </c>
       <c r="H156" t="n">
-        <v>0.03574730354391371</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>-212.83025</v>
+        <v>-133.794</v>
       </c>
       <c r="J156" t="n">
-        <v>-38.17450000000009</v>
+        <v>-54.63499999999999</v>
       </c>
       <c r="K156" t="b">
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>0.9642526964560862</v>
+        <v>1</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -9694,25 +9694,25 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>242.9625</v>
+        <v>-123.655</v>
       </c>
       <c r="G157" t="n">
-        <v>36.82407750000005</v>
+        <v>45.67149300000001</v>
       </c>
       <c r="H157" t="n">
-        <v>0.9953775038520801</v>
+        <v>0.01602136181575434</v>
       </c>
       <c r="I157" t="n">
-        <v>147.26325</v>
+        <v>-183.785</v>
       </c>
       <c r="J157" t="n">
-        <v>290.66825</v>
+        <v>-65.77200000000002</v>
       </c>
       <c r="K157" t="b">
         <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>0.9953775038520801</v>
+        <v>0.9839786381842457</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -9753,25 +9753,25 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>60.48999999999999</v>
+        <v>50.25</v>
       </c>
       <c r="G158" t="n">
-        <v>24.38877000000004</v>
+        <v>45.29343000000001</v>
       </c>
       <c r="H158" t="n">
-        <v>0.975860527492177</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="I158" t="n">
-        <v>11.11250000000001</v>
+        <v>-141.49</v>
       </c>
       <c r="J158" t="n">
-        <v>87.56750000000001</v>
+        <v>88.93499999999999</v>
       </c>
       <c r="K158" t="b">
         <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>0.975860527492177</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -9812,25 +9812,25 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>49.63499999999999</v>
+        <v>-166.58</v>
       </c>
       <c r="G159" t="n">
-        <v>70.08250199999996</v>
+        <v>245.985579</v>
       </c>
       <c r="H159" t="n">
-        <v>0.6443153032334973</v>
+        <v>0.3662426088514603</v>
       </c>
       <c r="I159" t="n">
-        <v>-344.22</v>
+        <v>-350.97</v>
       </c>
       <c r="J159" t="n">
-        <v>104.835</v>
+        <v>177.515</v>
       </c>
       <c r="K159" t="b">
         <v>0</v>
       </c>
       <c r="L159" t="n">
-        <v>0.6443153032334973</v>
+        <v>0.6337573911485397</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
@@ -9871,25 +9871,25 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>-89.19500000000002</v>
+        <v>-108.48</v>
       </c>
       <c r="G160" t="n">
-        <v>33.84775799999989</v>
+        <v>27.45033900000002</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1624199076143645</v>
+        <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>-125.6275</v>
+        <v>-132.78</v>
       </c>
       <c r="J160" t="n">
-        <v>84.93999999999997</v>
+        <v>-60.76500000000001</v>
       </c>
       <c r="K160" t="b">
         <v>0</v>
       </c>
       <c r="L160" t="n">
-        <v>0.8375800923856356</v>
+        <v>1</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
@@ -9930,25 +9930,25 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>-117.9399999999999</v>
+        <v>-114.2</v>
       </c>
       <c r="G161" t="n">
-        <v>31.49042400000001</v>
+        <v>34.80403499999995</v>
       </c>
       <c r="H161" t="n">
-        <v>0.09104455371777678</v>
+        <v>0.009496506002508511</v>
       </c>
       <c r="I161" t="n">
-        <v>-165.765</v>
+        <v>-173.255</v>
       </c>
       <c r="J161" t="n">
-        <v>92.32250000000002</v>
+        <v>-70.75999999999999</v>
       </c>
       <c r="K161" t="b">
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>0.9089554462822232</v>
+        <v>0.9905034939974915</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
@@ -9989,25 +9989,25 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>11.92750000000001</v>
+        <v>23</v>
       </c>
       <c r="G162" t="n">
-        <v>22.76161650000003</v>
+        <v>34.80403499999999</v>
       </c>
       <c r="H162" t="n">
-        <v>0.7406487917907978</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="I162" t="n">
-        <v>-17.60349999999999</v>
+        <v>-13.38700000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>65.71325</v>
+        <v>70.47675000000002</v>
       </c>
       <c r="K162" t="b">
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0.7406487917907978</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -10048,25 +10048,25 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>-69.05250000000001</v>
+        <v>-91.96000000000001</v>
       </c>
       <c r="G163" t="n">
-        <v>102.158553</v>
+        <v>127.8779565</v>
       </c>
       <c r="H163" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1776911733726564</v>
       </c>
       <c r="I163" t="n">
-        <v>-300.044</v>
+        <v>-350.886</v>
       </c>
       <c r="J163" t="n">
-        <v>52.63224999999998</v>
+        <v>51.18175000000004</v>
       </c>
       <c r="K163" t="b">
         <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8223088266273436</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -10107,19 +10107,19 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>-90.68999999999997</v>
+        <v>-97.04500000000002</v>
       </c>
       <c r="G164" t="n">
-        <v>16.89422700000001</v>
+        <v>25.59708900000002</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>-133.32175</v>
+        <v>-177.813</v>
       </c>
       <c r="J164" t="n">
-        <v>-58.66000000000003</v>
+        <v>-62.01474999999998</v>
       </c>
       <c r="K164" t="b">
         <v>0</v>
@@ -10166,25 +10166,25 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>-1.362499999999983</v>
+        <v>155.3800000000001</v>
       </c>
       <c r="G165" t="n">
-        <v>188.238309</v>
+        <v>164.8428809999999</v>
       </c>
       <c r="H165" t="n">
-        <v>0.4985104270109235</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="I165" t="n">
-        <v>-162.47425</v>
+        <v>-148.41225</v>
       </c>
       <c r="J165" t="n">
-        <v>279.87175</v>
+        <v>283.62575</v>
       </c>
       <c r="K165" t="b">
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0.5014895729890765</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -10225,25 +10225,25 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>52.69499999999999</v>
+        <v>54.27000000000001</v>
       </c>
       <c r="G166" t="n">
-        <v>55.69016250000002</v>
+        <v>23.38060200000001</v>
       </c>
       <c r="H166" t="n">
-        <v>0.6015037593984962</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="I166" t="n">
-        <v>-138.81575</v>
+        <v>13.31899999999999</v>
       </c>
       <c r="J166" t="n">
-        <v>93.33325000000001</v>
+        <v>84.059</v>
       </c>
       <c r="K166" t="b">
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>0.6015037593984962</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -10284,25 +10284,25 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>4.392499999999998</v>
+        <v>61.20000000000002</v>
       </c>
       <c r="G167" t="n">
-        <v>120.5390865</v>
+        <v>51.07556999999998</v>
       </c>
       <c r="H167" t="n">
-        <v>0.5335660580021482</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="I167" t="n">
-        <v>-329.376</v>
+        <v>-371.451</v>
       </c>
       <c r="J167" t="n">
-        <v>179.37675</v>
+        <v>103.878</v>
       </c>
       <c r="K167" t="b">
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>0.5335660580021482</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -10343,25 +10343,25 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>-100.8325</v>
+        <v>-89.66500000000002</v>
       </c>
       <c r="G168" t="n">
-        <v>35.37854249999995</v>
+        <v>53.82579300000009</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>0.1922349861858368</v>
       </c>
       <c r="I168" t="n">
-        <v>-133.995</v>
+        <v>-212.26</v>
       </c>
       <c r="J168" t="n">
-        <v>-56.57025000000002</v>
+        <v>89.24200000000005</v>
       </c>
       <c r="K168" t="b">
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>1</v>
+        <v>0.8077650138141632</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -10402,25 +10402,25 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>-117.52</v>
+        <v>-73.69</v>
       </c>
       <c r="G169" t="n">
-        <v>43.75152599999998</v>
+        <v>131.017362</v>
       </c>
       <c r="H169" t="n">
-        <v>0.008592910848549946</v>
+        <v>0.4561582085211575</v>
       </c>
       <c r="I169" t="n">
-        <v>-180.73975</v>
+        <v>-161.743</v>
       </c>
       <c r="J169" t="n">
-        <v>-68.88175000000004</v>
+        <v>272.212</v>
       </c>
       <c r="K169" t="b">
         <v>0</v>
       </c>
       <c r="L169" t="n">
-        <v>0.99140708915145</v>
+        <v>0.5438417914788425</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
@@ -10461,25 +10461,25 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>58.82999999999998</v>
+        <v>64.69999999999999</v>
       </c>
       <c r="G170" t="n">
-        <v>23.59557900000003</v>
+        <v>41.66847299999994</v>
       </c>
       <c r="H170" t="n">
-        <v>0.9958204125657274</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="I170" t="n">
-        <v>15.539</v>
+        <v>-132.525</v>
       </c>
       <c r="J170" t="n">
-        <v>86.063</v>
+        <v>96.30799999999999</v>
       </c>
       <c r="K170" t="b">
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>0.9958204125657274</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -10520,25 +10520,25 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>56.30500000000001</v>
+        <v>8.344999999999999</v>
       </c>
       <c r="G171" t="n">
-        <v>58.444092</v>
+        <v>59.51156399999994</v>
       </c>
       <c r="H171" t="n">
-        <v>0.6882836726439261</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="I171" t="n">
-        <v>-338.46</v>
+        <v>-49.76300000000003</v>
       </c>
       <c r="J171" t="n">
-        <v>103.72</v>
+        <v>171.043</v>
       </c>
       <c r="K171" t="b">
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>0.6882836726439261</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -10579,25 +10579,25 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>-86.41499999999996</v>
+        <v>-93.96000000000001</v>
       </c>
       <c r="G172" t="n">
-        <v>38.28073199999999</v>
+        <v>32.12052899999998</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1782391802615613</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>-125.389</v>
+        <v>-133.794</v>
       </c>
       <c r="J172" t="n">
-        <v>86.86799999999999</v>
+        <v>-54.63499999999999</v>
       </c>
       <c r="K172" t="b">
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>0.8217608197384387</v>
+        <v>1</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -10638,25 +10638,25 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>-110.835</v>
+        <v>-123.655</v>
       </c>
       <c r="G173" t="n">
-        <v>44.44093499999986</v>
+        <v>45.67149300000001</v>
       </c>
       <c r="H173" t="n">
-        <v>0.2505055952541459</v>
+        <v>0.01602136181575434</v>
       </c>
       <c r="I173" t="n">
-        <v>-162.081</v>
+        <v>-183.785</v>
       </c>
       <c r="J173" t="n">
-        <v>267.522</v>
+        <v>-65.77200000000002</v>
       </c>
       <c r="K173" t="b">
         <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>0.749494404745854</v>
+        <v>0.9839786381842457</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -10697,25 +10697,25 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>47.94249999999999</v>
+        <v>50.25</v>
       </c>
       <c r="G174" t="n">
-        <v>22.5244005</v>
+        <v>45.29343000000001</v>
       </c>
       <c r="H174" t="n">
-        <v>0.9611691022964509</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="I174" t="n">
-        <v>2.689250000000012</v>
+        <v>-141.49</v>
       </c>
       <c r="J174" t="n">
-        <v>73.30525</v>
+        <v>88.93499999999999</v>
       </c>
       <c r="K174" t="b">
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>0.9611691022964509</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
@@ -10756,25 +10756,25 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>-176.9625</v>
+        <v>-166.58</v>
       </c>
       <c r="G175" t="n">
-        <v>192.9047925</v>
+        <v>245.985579</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1125260960334029</v>
+        <v>0.3662426088514603</v>
       </c>
       <c r="I175" t="n">
-        <v>-391.7225</v>
+        <v>-350.97</v>
       </c>
       <c r="J175" t="n">
-        <v>58.79475000000001</v>
+        <v>177.515</v>
       </c>
       <c r="K175" t="b">
         <v>0</v>
       </c>
       <c r="L175" t="n">
-        <v>0.8874739039665971</v>
+        <v>0.6337573911485397</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -10815,19 +10815,19 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>-140.395</v>
+        <v>-108.48</v>
       </c>
       <c r="G176" t="n">
-        <v>51.96883650000001</v>
+        <v>27.45033900000002</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>-217.33475</v>
+        <v>-132.78</v>
       </c>
       <c r="J176" t="n">
-        <v>-78.63250000000001</v>
+        <v>-60.76500000000001</v>
       </c>
       <c r="K176" t="b">
         <v>0</v>
@@ -10874,25 +10874,25 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>230.4725</v>
+        <v>-114.2</v>
       </c>
       <c r="G177" t="n">
-        <v>38.23625399999999</v>
+        <v>34.80403499999995</v>
       </c>
       <c r="H177" t="n">
-        <v>0.9665970772442589</v>
+        <v>0.009496506002508511</v>
       </c>
       <c r="I177" t="n">
-        <v>41.53450000000002</v>
+        <v>-173.255</v>
       </c>
       <c r="J177" t="n">
-        <v>285.4615</v>
+        <v>-70.75999999999999</v>
       </c>
       <c r="K177" t="b">
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>0.9665970772442589</v>
+        <v>0.9905034939974915</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -10933,25 +10933,25 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>59.0975</v>
+        <v>23</v>
       </c>
       <c r="G178" t="n">
-        <v>23.61781799999997</v>
+        <v>34.80403499999999</v>
       </c>
       <c r="H178" t="n">
-        <v>0.9925373134328358</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="I178" t="n">
-        <v>14.65150000000003</v>
+        <v>-13.38700000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>86.45</v>
+        <v>70.47675000000002</v>
       </c>
       <c r="K178" t="b">
         <v>0</v>
       </c>
       <c r="L178" t="n">
-        <v>0.9925373134328358</v>
+        <v>0.8269433326311355</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -10992,25 +10992,25 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>55.6625</v>
+        <v>-91.96000000000001</v>
       </c>
       <c r="G179" t="n">
-        <v>59.548629</v>
+        <v>127.8779565</v>
       </c>
       <c r="H179" t="n">
-        <v>0.685367803837953</v>
+        <v>0.1776911733726564</v>
       </c>
       <c r="I179" t="n">
-        <v>-339.454</v>
+        <v>-350.886</v>
       </c>
       <c r="J179" t="n">
-        <v>103.7285</v>
+        <v>51.18175000000004</v>
       </c>
       <c r="K179" t="b">
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>0.685367803837953</v>
+        <v>0.8223088266273436</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -11051,25 +11051,25 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>-86.09999999999997</v>
+        <v>-97.04500000000002</v>
       </c>
       <c r="G180" t="n">
-        <v>38.11393950000004</v>
+        <v>25.59708900000002</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1761727078891258</v>
+        <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>-124.71625</v>
+        <v>-177.813</v>
       </c>
       <c r="J180" t="n">
-        <v>86.63924999999992</v>
+        <v>-62.01474999999998</v>
       </c>
       <c r="K180" t="b">
         <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>0.8238272921108742</v>
+        <v>1</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -11110,25 +11110,25 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>-111.305</v>
+        <v>155.3800000000001</v>
       </c>
       <c r="G181" t="n">
-        <v>44.02580700000007</v>
+        <v>164.8428809999999</v>
       </c>
       <c r="H181" t="n">
-        <v>0.2464019189765458</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="I181" t="n">
-        <v>-163.2835</v>
+        <v>-148.41225</v>
       </c>
       <c r="J181" t="n">
-        <v>267.372</v>
+        <v>283.62575</v>
       </c>
       <c r="K181" t="b">
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>0.7535980810234542</v>
+        <v>0.6650516115441332</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
@@ -11169,25 +11169,25 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>14.97499999999997</v>
+        <v>54.27000000000001</v>
       </c>
       <c r="G182" t="n">
-        <v>27.39103499999995</v>
+        <v>23.38060200000001</v>
       </c>
       <c r="H182" t="n">
-        <v>0.7754375096794177</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="I182" t="n">
-        <v>-16.77300000000001</v>
+        <v>13.31899999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>70.154</v>
+        <v>84.059</v>
       </c>
       <c r="K182" t="b">
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>0.7754375096794177</v>
+        <v>0.9824051185109787</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
@@ -11228,25 +11228,25 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>-69.435</v>
+        <v>61.20000000000002</v>
       </c>
       <c r="G183" t="n">
-        <v>102.188205</v>
+        <v>51.07556999999998</v>
       </c>
       <c r="H183" t="n">
-        <v>0.2072169738268546</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="I183" t="n">
-        <v>-305.437</v>
+        <v>-371.451</v>
       </c>
       <c r="J183" t="n">
-        <v>50.47999999999999</v>
+        <v>103.878</v>
       </c>
       <c r="K183" t="b">
         <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>0.7927830261731454</v>
+        <v>0.7218263777810091</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
@@ -11287,25 +11287,25 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>-89.41500000000002</v>
+        <v>-89.66500000000002</v>
       </c>
       <c r="G184" t="n">
-        <v>15.55247400000001</v>
+        <v>53.82579300000009</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>0.1922349861858368</v>
       </c>
       <c r="I184" t="n">
-        <v>-119.961</v>
+        <v>-212.26</v>
       </c>
       <c r="J184" t="n">
-        <v>-59.03000000000002</v>
+        <v>89.24200000000005</v>
       </c>
       <c r="K184" t="b">
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>1</v>
+        <v>0.8077650138141632</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
@@ -11346,25 +11346,25 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>78.06</v>
+        <v>-73.69</v>
       </c>
       <c r="G185" t="n">
-        <v>224.999376</v>
+        <v>131.017362</v>
       </c>
       <c r="H185" t="n">
-        <v>0.5821588973207372</v>
+        <v>0.4561582085211575</v>
       </c>
       <c r="I185" t="n">
-        <v>-159.186</v>
+        <v>-161.743</v>
       </c>
       <c r="J185" t="n">
-        <v>287.315</v>
+        <v>272.212</v>
       </c>
       <c r="K185" t="b">
         <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0.5821588973207372</v>
+        <v>0.5438417914788425</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
@@ -11405,25 +11405,25 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>52.245</v>
+        <v>64.69999999999999</v>
       </c>
       <c r="G186" t="n">
-        <v>56.30173499999994</v>
+        <v>41.66847299999994</v>
       </c>
       <c r="H186" t="n">
-        <v>0.5984445354072861</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="I186" t="n">
-        <v>-139</v>
+        <v>-132.525</v>
       </c>
       <c r="J186" t="n">
-        <v>93.23799999999999</v>
+        <v>96.30799999999999</v>
       </c>
       <c r="K186" t="b">
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0.5984445354072861</v>
+        <v>0.6165554072096128</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -11464,25 +11464,25 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>4.474999999999994</v>
+        <v>8.344999999999999</v>
       </c>
       <c r="G187" t="n">
-        <v>118.519044</v>
+        <v>59.51156399999994</v>
       </c>
       <c r="H187" t="n">
-        <v>0.5351343975985809</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="I187" t="n">
-        <v>-328.827</v>
+        <v>-49.76300000000003</v>
       </c>
       <c r="J187" t="n">
-        <v>179.474</v>
+        <v>171.043</v>
       </c>
       <c r="K187" t="b">
         <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>0.5351343975985809</v>
+        <v>0.5861148197596796</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
@@ -11523,19 +11523,19 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>-101.2</v>
+        <v>-93.96000000000001</v>
       </c>
       <c r="G188" t="n">
-        <v>35.33777099999993</v>
+        <v>32.12052899999998</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>-134.038</v>
+        <v>-133.794</v>
       </c>
       <c r="J188" t="n">
-        <v>-56.489</v>
+        <v>-54.63499999999999</v>
       </c>
       <c r="K188" t="b">
         <v>0</v>
@@ -11582,25 +11582,25 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>-117.235</v>
+        <v>-123.655</v>
       </c>
       <c r="G189" t="n">
-        <v>43.58844000000005</v>
+        <v>45.67149300000001</v>
       </c>
       <c r="H189" t="n">
-        <v>0.008186655751125664</v>
+        <v>0.01602136181575434</v>
       </c>
       <c r="I189" t="n">
-        <v>-180.456</v>
+        <v>-183.785</v>
       </c>
       <c r="J189" t="n">
-        <v>-68.88900000000001</v>
+        <v>-65.77200000000002</v>
       </c>
       <c r="K189" t="b">
         <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>0.9918133442488744</v>
+        <v>0.9839786381842457</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -11641,25 +11641,25 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>44.56999999999999</v>
+        <v>50.25</v>
       </c>
       <c r="G190" t="n">
-        <v>24.04777200000004</v>
+        <v>45.29343000000001</v>
       </c>
       <c r="H190" t="n">
-        <v>0.9312457454050375</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="I190" t="n">
-        <v>-3.199000000000011</v>
+        <v>-141.49</v>
       </c>
       <c r="J190" t="n">
-        <v>71.49099999999997</v>
+        <v>88.93499999999999</v>
       </c>
       <c r="K190" t="b">
         <v>0</v>
       </c>
       <c r="L190" t="n">
-        <v>0.9312457454050375</v>
+        <v>0.7219136355491848</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -11700,25 +11700,25 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>-197.245</v>
+        <v>-166.58</v>
       </c>
       <c r="G191" t="n">
-        <v>180.387942</v>
+        <v>245.985579</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1105060131608804</v>
+        <v>0.3662426088514603</v>
       </c>
       <c r="I191" t="n">
-        <v>-392.208</v>
+        <v>-350.97</v>
       </c>
       <c r="J191" t="n">
-        <v>64.70299999999996</v>
+        <v>177.515</v>
       </c>
       <c r="K191" t="b">
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0.8894939868391196</v>
+        <v>0.6337573911485397</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -11759,19 +11759,19 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>-155.745</v>
+        <v>-108.48</v>
       </c>
       <c r="G192" t="n">
-        <v>48.1845</v>
+        <v>27.45033900000002</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>-217.9535</v>
+        <v>-132.78</v>
       </c>
       <c r="J192" t="n">
-        <v>-103.193</v>
+        <v>-60.76500000000001</v>
       </c>
       <c r="K192" t="b">
         <v>0</v>
@@ -11818,25 +11818,25 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>225.775</v>
+        <v>-114.2</v>
       </c>
       <c r="G193" t="n">
-        <v>42.31340399999998</v>
+        <v>34.80403499999995</v>
       </c>
       <c r="H193" t="n">
-        <v>0.8840481052870434</v>
+        <v>0.009496506002508511</v>
       </c>
       <c r="I193" t="n">
-        <v>-108.189</v>
+        <v>-173.255</v>
       </c>
       <c r="J193" t="n">
-        <v>279.1555</v>
+        <v>-70.75999999999999</v>
       </c>
       <c r="K193" t="b">
         <v>0</v>
       </c>
       <c r="L193" t="n">
-        <v>0.8840481052870434</v>
+        <v>0.9905034939974915</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -11877,25 +11877,25 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="G194" t="n">
         <v>0.3261720000000001</v>
       </c>
       <c r="H194" t="n">
-        <v>0.9339814814814815</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.04499999999999993</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>1.055</v>
+        <v>1.07</v>
       </c>
       <c r="K194" t="b">
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>0.9339814814814815</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -11936,25 +11936,25 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0.3199999999999998</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="G195" t="n">
-        <v>0.3558240000000003</v>
+        <v>0.3409980000000003</v>
       </c>
       <c r="H195" t="n">
-        <v>0.7897222222222222</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4300000000000002</v>
+        <v>-0.3717499999999999</v>
       </c>
       <c r="J195" t="n">
-        <v>0.8750000000000001</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K195" t="b">
         <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>0.7897222222222222</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -11995,25 +11995,25 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>-1.205</v>
+        <v>-1.2</v>
       </c>
       <c r="G196" t="n">
         <v>0.185325</v>
       </c>
       <c r="H196" t="n">
-        <v>9.259259259259259e-05</v>
+        <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>-1.59</v>
+        <v>-1.585</v>
       </c>
       <c r="J196" t="n">
-        <v>-0.805</v>
+        <v>-0.78</v>
       </c>
       <c r="K196" t="b">
         <v>1</v>
       </c>
       <c r="L196" t="n">
-        <v>0.9999074074074074</v>
+        <v>1</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
@@ -12054,25 +12054,25 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>0.2500000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="G197" t="n">
-        <v>0.526323</v>
+        <v>0.548562</v>
       </c>
       <c r="H197" t="n">
-        <v>0.6611111111111111</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.7449999999999999</v>
+        <v>-0.765</v>
       </c>
       <c r="J197" t="n">
-        <v>1.07</v>
+        <v>1.105</v>
       </c>
       <c r="K197" t="b">
         <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>0.6611111111111111</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
@@ -12113,25 +12113,25 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="G198" t="n">
-        <v>0.7857779999999996</v>
+        <v>0.6597570000000001</v>
       </c>
       <c r="H198" t="n">
-        <v>0.7887037037037037</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.50025</v>
+        <v>-0.5</v>
       </c>
       <c r="J198" t="n">
-        <v>2.575</v>
+        <v>2.561750000000002</v>
       </c>
       <c r="K198" t="b">
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>0.7887037037037037</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -12172,25 +12172,25 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>-1.225</v>
+        <v>-1.145</v>
       </c>
       <c r="G199" t="n">
-        <v>0.6078660000000001</v>
+        <v>0.4373669999999997</v>
       </c>
       <c r="H199" t="n">
-        <v>0.006111111111111111</v>
+        <v>0.006951759005687803</v>
       </c>
       <c r="I199" t="n">
-        <v>-3.23</v>
+        <v>-3.095</v>
       </c>
       <c r="J199" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K199" t="b">
         <v>1</v>
       </c>
       <c r="L199" t="n">
-        <v>0.9938888888888889</v>
+        <v>0.9930482409943122</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -12231,25 +12231,25 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.4750000000000002</v>
       </c>
       <c r="G200" t="n">
-        <v>0.4892579999999994</v>
+        <v>0.4077149999999997</v>
       </c>
       <c r="H200" t="n">
-        <v>0.8318103940605368</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.25</v>
+        <v>-0.196</v>
       </c>
       <c r="J200" t="n">
-        <v>1.524749999999999</v>
+        <v>1.065</v>
       </c>
       <c r="K200" t="b">
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0.8318103940605368</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -12290,25 +12290,25 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1.22</v>
+        <v>1.175</v>
       </c>
       <c r="G201" t="n">
-        <v>0.6078659999999996</v>
+        <v>0.8895600000000005</v>
       </c>
       <c r="H201" t="n">
-        <v>0.9366076527698458</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1200000000000001</v>
+        <v>-0.2399999999999998</v>
       </c>
       <c r="J201" t="n">
-        <v>2.055</v>
+        <v>2.325</v>
       </c>
       <c r="K201" t="b">
         <v>0</v>
       </c>
       <c r="L201" t="n">
-        <v>0.9366076527698458</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -12349,25 +12349,25 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>-2.57</v>
+        <v>-2.33</v>
       </c>
       <c r="G202" t="n">
-        <v>0.4892580000000001</v>
+        <v>1.008168</v>
       </c>
       <c r="H202" t="n">
-        <v>0</v>
+        <v>0.0001454122437109205</v>
       </c>
       <c r="I202" t="n">
-        <v>-3.315</v>
+        <v>-3.45</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.77</v>
+        <v>-1.08</v>
       </c>
       <c r="K202" t="b">
         <v>1</v>
       </c>
       <c r="L202" t="n">
-        <v>1</v>
+        <v>0.9998545877562891</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
@@ -12408,25 +12408,25 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>0.335</v>
+        <v>0.365</v>
       </c>
       <c r="G203" t="n">
-        <v>0.4596060000000001</v>
+        <v>0.3261720000000003</v>
       </c>
       <c r="H203" t="n">
-        <v>0.7775556824671617</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.4350000000000002</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>1.164749999999999</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="K203" t="b">
         <v>0</v>
       </c>
       <c r="L203" t="n">
-        <v>0.7775556824671617</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
@@ -12467,25 +12467,25 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2.524999999999999</v>
+        <v>2.445</v>
       </c>
       <c r="G204" t="n">
-        <v>0.7746584999999999</v>
+        <v>0.7561259999999996</v>
       </c>
       <c r="H204" t="n">
-        <v>0.9994288977727013</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="I204" t="n">
-        <v>1.23525</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>3.93</v>
+        <v>3.464999999999999</v>
       </c>
       <c r="K204" t="b">
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>0.9994288977727013</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
@@ -12526,19 +12526,19 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>-3.82</v>
+        <v>-3.335</v>
       </c>
       <c r="G205" t="n">
-        <v>0.6301049999999997</v>
+        <v>0.6523440000000006</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>-4.779749999999999</v>
+        <v>-4.17</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.66</v>
+        <v>-2.04</v>
       </c>
       <c r="K205" t="b">
         <v>1</v>
@@ -12585,25 +12585,25 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>0.3400000000000003</v>
+        <v>0.41</v>
       </c>
       <c r="G206" t="n">
-        <v>0.4077150000000002</v>
+        <v>0.4966710000000001</v>
       </c>
       <c r="H206" t="n">
-        <v>0.8498921639108555</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.185</v>
+        <v>-0.2439999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>1.05</v>
+        <v>1.698999999999999</v>
       </c>
       <c r="K206" t="b">
         <v>0</v>
       </c>
       <c r="L206" t="n">
-        <v>0.8498921639108555</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
@@ -12644,25 +12644,25 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1.365</v>
+        <v>1.19</v>
       </c>
       <c r="G207" t="n">
-        <v>0.6449310000000004</v>
+        <v>0.6226919999999992</v>
       </c>
       <c r="H207" t="n">
-        <v>0.9718188353702373</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2300000000000001</v>
+        <v>-0.2299999999999997</v>
       </c>
       <c r="J207" t="n">
-        <v>2.365</v>
+        <v>2.05</v>
       </c>
       <c r="K207" t="b">
         <v>0</v>
       </c>
       <c r="L207" t="n">
-        <v>0.9718188353702373</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
@@ -12703,19 +12703,19 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>-2.54</v>
+        <v>-2.555</v>
       </c>
       <c r="G208" t="n">
-        <v>0.7413</v>
+        <v>0.5040839999999998</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>-3.485</v>
+        <v>-3.305</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.363500000000003</v>
+        <v>-1.735</v>
       </c>
       <c r="K208" t="b">
         <v>1</v>
@@ -12762,25 +12762,25 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>0.3099999999999998</v>
+        <v>0.2949999999999999</v>
       </c>
       <c r="G209" t="n">
-        <v>0.3484110000000003</v>
+        <v>0.4892579999999997</v>
       </c>
       <c r="H209" t="n">
-        <v>0.7703810208483106</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.26</v>
+        <v>-0.5950000000000002</v>
       </c>
       <c r="J209" t="n">
-        <v>0.84</v>
+        <v>1.133999999999998</v>
       </c>
       <c r="K209" t="b">
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>0.7703810208483106</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
@@ -12821,25 +12821,25 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>2.71</v>
+        <v>2.545</v>
       </c>
       <c r="G210" t="n">
-        <v>0.6523440000000006</v>
+        <v>0.7783649999999999</v>
       </c>
       <c r="H210" t="n">
-        <v>0.9992810927390366</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="I210" t="n">
-        <v>1.4535</v>
+        <v>1.235</v>
       </c>
       <c r="J210" t="n">
-        <v>3.815</v>
+        <v>3.925</v>
       </c>
       <c r="K210" t="b">
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>0.9992810927390366</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
@@ -12880,19 +12880,19 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>-3.485</v>
+        <v>-3.785</v>
       </c>
       <c r="G211" t="n">
-        <v>0.5633880000000011</v>
+        <v>0.6449310000000007</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>-4.265000000000001</v>
+        <v>-4.77</v>
       </c>
       <c r="J211" t="n">
-        <v>-2.295</v>
+        <v>-2.551000000000001</v>
       </c>
       <c r="K211" t="b">
         <v>1</v>
@@ -12939,25 +12939,25 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="G212" t="n">
-        <v>0.3632370000000001</v>
+        <v>0.3113460000000001</v>
       </c>
       <c r="H212" t="n">
-        <v>0.9828828828828828</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="I212" t="n">
-        <v>0.11</v>
+        <v>0.004999999999999893</v>
       </c>
       <c r="J212" t="n">
-        <v>2.665250000000001</v>
+        <v>2.24</v>
       </c>
       <c r="K212" t="b">
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0.9828828828828828</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
@@ -12998,25 +12998,25 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1.09</v>
+        <v>1.185</v>
       </c>
       <c r="G213" t="n">
-        <v>0.585627</v>
+        <v>0.5782140000000004</v>
       </c>
       <c r="H213" t="n">
-        <v>0.9081081081081082</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.45525</v>
+        <v>-0.165</v>
       </c>
       <c r="J213" t="n">
-        <v>1.985</v>
+        <v>2.135</v>
       </c>
       <c r="K213" t="b">
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>0.9081081081081082</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
@@ -13057,19 +13057,19 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>-2.36</v>
+        <v>-2.38</v>
       </c>
       <c r="G214" t="n">
-        <v>0.5114970000000003</v>
+        <v>0.5485620000000001</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>-3.19025</v>
+        <v>-3.275</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.595</v>
+        <v>-1.58</v>
       </c>
       <c r="K214" t="b">
         <v>1</v>
@@ -13116,25 +13116,25 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>0.05999999999999994</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="G215" t="n">
-        <v>0.2372160000000002</v>
+        <v>0.214977</v>
       </c>
       <c r="H215" t="n">
-        <v>0.5950450450450451</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.49</v>
+        <v>-0.38</v>
       </c>
       <c r="J215" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="K215" t="b">
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>0.5950450450450451</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
@@ -13175,19 +13175,19 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>2.98</v>
+        <v>3.024999999999999</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7042349999999994</v>
+        <v>0.6745830000000014</v>
       </c>
       <c r="H216" t="n">
         <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>1.65</v>
+        <v>1.725</v>
       </c>
       <c r="J216" t="n">
-        <v>3.965</v>
+        <v>4.175000000000001</v>
       </c>
       <c r="K216" t="b">
         <v>0</v>
@@ -13234,19 +13234,19 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>-3.695</v>
+        <v>-3.655</v>
       </c>
       <c r="G217" t="n">
-        <v>0.7413000000000006</v>
+        <v>0.7190610000000004</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
       </c>
       <c r="I217" t="n">
-        <v>-4.720250000000001</v>
+        <v>-4.665</v>
       </c>
       <c r="J217" t="n">
-        <v>-2.339749999999999</v>
+        <v>-2.42</v>
       </c>
       <c r="K217" t="b">
         <v>1</v>
@@ -13293,25 +13293,25 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="G218" t="n">
-        <v>0.355824</v>
+        <v>0.3261720000000001</v>
       </c>
       <c r="H218" t="n">
-        <v>0.9224526600541028</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.07499999999999996</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="J218" t="n">
-        <v>1.155</v>
+        <v>1.07</v>
       </c>
       <c r="K218" t="b">
         <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>0.9224526600541028</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
@@ -13352,25 +13352,25 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>0.2999999999999998</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="G219" t="n">
         <v>0.3409980000000003</v>
       </c>
       <c r="H219" t="n">
-        <v>0.774721971746318</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4799999999999999</v>
+        <v>-0.3717499999999999</v>
       </c>
       <c r="J219" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K219" t="b">
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0.774721971746318</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
@@ -13411,25 +13411,25 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>-1.19</v>
+        <v>-1.2</v>
       </c>
       <c r="G220" t="n">
-        <v>0.170499</v>
+        <v>0.185325</v>
       </c>
       <c r="H220" t="n">
-        <v>0.0001502855425308085</v>
+        <v>0</v>
       </c>
       <c r="I220" t="n">
-        <v>-1.545</v>
+        <v>-1.585</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.83</v>
+        <v>-0.78</v>
       </c>
       <c r="K220" t="b">
         <v>1</v>
       </c>
       <c r="L220" t="n">
-        <v>0.9998497144574692</v>
+        <v>1</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
@@ -13470,25 +13470,25 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>0.4199999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="G221" t="n">
-        <v>0.400302</v>
+        <v>0.548562</v>
       </c>
       <c r="H221" t="n">
-        <v>0.8325819056206792</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.415</v>
+        <v>-0.765</v>
       </c>
       <c r="J221" t="n">
-        <v>1.175</v>
+        <v>1.105</v>
       </c>
       <c r="K221" t="b">
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0.8325819056206792</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -13529,25 +13529,25 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>0.2549999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G222" t="n">
-        <v>0.4151280000000002</v>
+        <v>0.6597570000000001</v>
       </c>
       <c r="H222" t="n">
-        <v>0.7085963330327623</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="J222" t="n">
-        <v>2.591749999999997</v>
+        <v>2.561750000000002</v>
       </c>
       <c r="K222" t="b">
         <v>0</v>
       </c>
       <c r="L222" t="n">
-        <v>0.7085963330327623</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -13588,25 +13588,25 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>-1.025</v>
+        <v>-1.145</v>
       </c>
       <c r="G223" t="n">
-        <v>0.229803</v>
+        <v>0.4373669999999997</v>
       </c>
       <c r="H223" t="n">
-        <v>0.009918845807033363</v>
+        <v>0.006951759005687803</v>
       </c>
       <c r="I223" t="n">
-        <v>-3.175</v>
+        <v>-3.095</v>
       </c>
       <c r="J223" t="n">
-        <v>-0.4600000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K223" t="b">
         <v>1</v>
       </c>
       <c r="L223" t="n">
-        <v>0.9900811541929666</v>
+        <v>0.9930482409943122</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
@@ -13647,25 +13647,25 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>0.525</v>
+        <v>0.4750000000000002</v>
       </c>
       <c r="G224" t="n">
-        <v>0.5114970000000001</v>
+        <v>0.4077149999999997</v>
       </c>
       <c r="H224" t="n">
-        <v>0.8987444969835318</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.145</v>
+        <v>-0.196</v>
       </c>
       <c r="J224" t="n">
-        <v>2.395</v>
+        <v>1.065</v>
       </c>
       <c r="K224" t="b">
         <v>0</v>
       </c>
       <c r="L224" t="n">
-        <v>0.8987444969835318</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
@@ -13706,25 +13706,25 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>1.085</v>
+        <v>1.175</v>
       </c>
       <c r="G225" t="n">
-        <v>0.6152789999999997</v>
+        <v>0.8895600000000005</v>
       </c>
       <c r="H225" t="n">
-        <v>0.8976031306049241</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4369999999999999</v>
+        <v>-0.2399999999999998</v>
       </c>
       <c r="J225" t="n">
-        <v>1.975</v>
+        <v>2.325</v>
       </c>
       <c r="K225" t="b">
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0.8976031306049241</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
@@ -13765,25 +13765,25 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>-2.48</v>
+        <v>-2.33</v>
       </c>
       <c r="G226" t="n">
-        <v>0.5040839999999991</v>
+        <v>1.008168</v>
       </c>
       <c r="H226" t="n">
-        <v>0</v>
+        <v>0.0001454122437109205</v>
       </c>
       <c r="I226" t="n">
-        <v>-3.27</v>
+        <v>-3.45</v>
       </c>
       <c r="J226" t="n">
-        <v>-1.71</v>
+        <v>-1.08</v>
       </c>
       <c r="K226" t="b">
         <v>1</v>
       </c>
       <c r="L226" t="n">
-        <v>1</v>
+        <v>0.9998545877562891</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
@@ -13824,25 +13824,25 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>0.145</v>
+        <v>0.365</v>
       </c>
       <c r="G227" t="n">
-        <v>0.3928890000000002</v>
+        <v>0.3261720000000003</v>
       </c>
       <c r="H227" t="n">
-        <v>0.6619924995923692</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.53</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="J227" t="n">
-        <v>0.98</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="K227" t="b">
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>0.6619924995923692</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -13883,25 +13883,25 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>2.755</v>
+        <v>2.445</v>
       </c>
       <c r="G228" t="n">
-        <v>0.8376689999999992</v>
+        <v>0.7561259999999996</v>
       </c>
       <c r="H228" t="n">
-        <v>0.9996738953203979</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="I228" t="n">
-        <v>1.425</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>4.02</v>
+        <v>3.464999999999999</v>
       </c>
       <c r="K228" t="b">
         <v>0</v>
       </c>
       <c r="L228" t="n">
-        <v>0.9996738953203979</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
@@ -13942,19 +13942,19 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>-3.805</v>
+        <v>-3.335</v>
       </c>
       <c r="G229" t="n">
-        <v>0.6894090000000004</v>
+        <v>0.6523440000000006</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>-4.782</v>
+        <v>-4.17</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.47</v>
+        <v>-2.04</v>
       </c>
       <c r="K229" t="b">
         <v>1</v>
@@ -14001,25 +14001,25 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="G230" t="n">
-        <v>0.3632369999999993</v>
+        <v>0.4966710000000001</v>
       </c>
       <c r="H230" t="n">
-        <v>0.8751579189158148</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.155</v>
+        <v>-0.2439999999999999</v>
       </c>
       <c r="J230" t="n">
-        <v>1.015</v>
+        <v>1.698999999999999</v>
       </c>
       <c r="K230" t="b">
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>0.8751579189158148</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
@@ -14060,25 +14060,25 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>1.365</v>
+        <v>1.19</v>
       </c>
       <c r="G231" t="n">
         <v>0.6226919999999992</v>
       </c>
       <c r="H231" t="n">
-        <v>0.9792121281727346</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="I231" t="n">
-        <v>0.2950000000000001</v>
+        <v>-0.2299999999999997</v>
       </c>
       <c r="J231" t="n">
-        <v>2.335</v>
+        <v>2.05</v>
       </c>
       <c r="K231" t="b">
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0.9792121281727346</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -14119,19 +14119,19 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>-2.495</v>
+        <v>-2.555</v>
       </c>
       <c r="G232" t="n">
-        <v>0.7042350000000007</v>
+        <v>0.5040839999999998</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>-3.455000000000001</v>
+        <v>-3.305</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.405</v>
+        <v>-1.735</v>
       </c>
       <c r="K232" t="b">
         <v>1</v>
@@ -14178,25 +14178,25 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>0.2450000000000001</v>
+        <v>0.2949999999999999</v>
       </c>
       <c r="G233" t="n">
-        <v>0.348411</v>
+        <v>0.4892579999999997</v>
       </c>
       <c r="H233" t="n">
-        <v>0.7627196508556334</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.245</v>
+        <v>-0.5950000000000002</v>
       </c>
       <c r="J233" t="n">
-        <v>0.8034999999999946</v>
+        <v>1.133999999999998</v>
       </c>
       <c r="K233" t="b">
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>0.7627196508556334</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
@@ -14237,25 +14237,25 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>2.75</v>
+        <v>2.545</v>
       </c>
       <c r="G234" t="n">
-        <v>0.6523440000000006</v>
+        <v>0.7783649999999999</v>
       </c>
       <c r="H234" t="n">
-        <v>0.9998851498794074</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="I234" t="n">
-        <v>1.485</v>
+        <v>1.235</v>
       </c>
       <c r="J234" t="n">
-        <v>3.78</v>
+        <v>3.925</v>
       </c>
       <c r="K234" t="b">
         <v>0</v>
       </c>
       <c r="L234" t="n">
-        <v>0.9998851498794074</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
@@ -14296,19 +14296,19 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>-3.515000000000001</v>
+        <v>-3.785</v>
       </c>
       <c r="G235" t="n">
-        <v>0.5856269999999993</v>
+        <v>0.6449310000000007</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>-4.3485</v>
+        <v>-4.77</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.32</v>
+        <v>-2.551000000000001</v>
       </c>
       <c r="K235" t="b">
         <v>1</v>
@@ -14355,25 +14355,25 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>0.355</v>
+        <v>0.4</v>
       </c>
       <c r="G236" t="n">
-        <v>0.266868</v>
+        <v>0.3113460000000001</v>
       </c>
       <c r="H236" t="n">
-        <v>0.9528907922912205</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="I236" t="n">
-        <v>0.009999999999999959</v>
+        <v>0.004999999999999893</v>
       </c>
       <c r="J236" t="n">
-        <v>0.8644999999999982</v>
+        <v>2.24</v>
       </c>
       <c r="K236" t="b">
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>0.9528907922912205</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
@@ -14414,25 +14414,25 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>0.3500000000000001</v>
+        <v>1.185</v>
       </c>
       <c r="G237" t="n">
-        <v>0.385476</v>
+        <v>0.5782140000000004</v>
       </c>
       <c r="H237" t="n">
-        <v>0.8122769450392576</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.3400000000000002</v>
+        <v>-0.165</v>
       </c>
       <c r="J237" t="n">
-        <v>0.945</v>
+        <v>2.135</v>
       </c>
       <c r="K237" t="b">
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>0.8122769450392576</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -14473,19 +14473,19 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>-1.235</v>
+        <v>-2.38</v>
       </c>
       <c r="G238" t="n">
-        <v>0.2149769999999997</v>
+        <v>0.5485620000000001</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>-1.65</v>
+        <v>-3.275</v>
       </c>
       <c r="J238" t="n">
-        <v>-0.765</v>
+        <v>-1.58</v>
       </c>
       <c r="K238" t="b">
         <v>1</v>
@@ -14532,25 +14532,25 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>-0.15</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="G239" t="n">
-        <v>0.5114969999999998</v>
+        <v>0.214977</v>
       </c>
       <c r="H239" t="n">
-        <v>0.3859148227456579</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.9750000000000001</v>
+        <v>-0.38</v>
       </c>
       <c r="J239" t="n">
-        <v>0.6900000000000003</v>
+        <v>0.425</v>
       </c>
       <c r="K239" t="b">
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0.6140851772543421</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
@@ -14591,25 +14591,25 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>1.61</v>
+        <v>3.024999999999999</v>
       </c>
       <c r="G240" t="n">
-        <v>0.9414509999999996</v>
+        <v>0.6745830000000014</v>
       </c>
       <c r="H240" t="n">
-        <v>0.9174399238639067</v>
+        <v>1</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3394999999999997</v>
+        <v>1.725</v>
       </c>
       <c r="J240" t="n">
-        <v>2.584499999999998</v>
+        <v>4.175000000000001</v>
       </c>
       <c r="K240" t="b">
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>0.9174399238639067</v>
+        <v>1</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
@@ -14650,19 +14650,19 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>-2.4</v>
+        <v>-3.655</v>
       </c>
       <c r="G241" t="n">
-        <v>0.5930399999999998</v>
+        <v>0.7190610000000004</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
       </c>
       <c r="I241" t="n">
-        <v>-3.27</v>
+        <v>-4.665</v>
       </c>
       <c r="J241" t="n">
-        <v>-1.26</v>
+        <v>-2.42</v>
       </c>
       <c r="K241" t="b">
         <v>1</v>
@@ -14709,16 +14709,16 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>0.435</v>
+        <v>0.42</v>
       </c>
       <c r="G242" t="n">
-        <v>0.333585</v>
+        <v>0.3261720000000001</v>
       </c>
       <c r="H242" t="n">
-        <v>0.9385693671407958</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.02500000000000002</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="J242" t="n">
         <v>1.07</v>
@@ -14727,7 +14727,7 @@
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0.9385693671407958</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
@@ -14768,25 +14768,25 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>0.345</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="G243" t="n">
         <v>0.3409980000000003</v>
       </c>
       <c r="H243" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.355</v>
+        <v>-0.3717499999999999</v>
       </c>
       <c r="J243" t="n">
-        <v>0.895</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K243" t="b">
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
@@ -14833,19 +14833,19 @@
         <v>0.185325</v>
       </c>
       <c r="H244" t="n">
-        <v>0.0001030715316429602</v>
+        <v>0</v>
       </c>
       <c r="I244" t="n">
         <v>-1.585</v>
       </c>
       <c r="J244" t="n">
-        <v>-0.805</v>
+        <v>-0.78</v>
       </c>
       <c r="K244" t="b">
         <v>1</v>
       </c>
       <c r="L244" t="n">
-        <v>0.9998969284683571</v>
+        <v>1</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
@@ -14886,25 +14886,25 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>0.235</v>
+        <v>0.255</v>
       </c>
       <c r="G245" t="n">
-        <v>0.533736</v>
+        <v>0.548562</v>
       </c>
       <c r="H245" t="n">
-        <v>0.65007215007215</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.7450000000000001</v>
+        <v>-0.765</v>
       </c>
       <c r="J245" t="n">
-        <v>1.075</v>
+        <v>1.105</v>
       </c>
       <c r="K245" t="b">
         <v>0</v>
       </c>
       <c r="L245" t="n">
-        <v>0.65007215007215</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
@@ -14945,25 +14945,25 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>0.455</v>
+        <v>0.4</v>
       </c>
       <c r="G246" t="n">
-        <v>0.748713</v>
+        <v>0.6597570000000001</v>
       </c>
       <c r="H246" t="n">
-        <v>0.8028241599670171</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4199999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="J246" t="n">
-        <v>2.635</v>
+        <v>2.561750000000002</v>
       </c>
       <c r="K246" t="b">
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>0.8028241599670171</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
@@ -15004,25 +15004,25 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>-1.165</v>
+        <v>-1.145</v>
       </c>
       <c r="G247" t="n">
-        <v>0.4818450000000001</v>
+        <v>0.4373669999999997</v>
       </c>
       <c r="H247" t="n">
-        <v>0.006802721088435374</v>
+        <v>0.006951759005687803</v>
       </c>
       <c r="I247" t="n">
-        <v>-3.255</v>
+        <v>-3.095</v>
       </c>
       <c r="J247" t="n">
-        <v>-0.575</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K247" t="b">
         <v>1</v>
       </c>
       <c r="L247" t="n">
-        <v>0.9931972789115646</v>
+        <v>0.9930482409943122</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
@@ -15063,25 +15063,25 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>0.5299999999999999</v>
+        <v>0.4750000000000002</v>
       </c>
       <c r="G248" t="n">
-        <v>0.5411489999999998</v>
+        <v>0.4077149999999997</v>
       </c>
       <c r="H248" t="n">
-        <v>0.889049512106975</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.17</v>
+        <v>-0.196</v>
       </c>
       <c r="J248" t="n">
-        <v>2.485249999999992</v>
+        <v>1.065</v>
       </c>
       <c r="K248" t="b">
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0.889049512106975</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
@@ -15122,25 +15122,25 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>1.1</v>
+        <v>1.175</v>
       </c>
       <c r="G249" t="n">
-        <v>0.644931</v>
+        <v>0.8895600000000005</v>
       </c>
       <c r="H249" t="n">
-        <v>0.8877846042645464</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.47675</v>
+        <v>-0.2399999999999998</v>
       </c>
       <c r="J249" t="n">
-        <v>1.985</v>
+        <v>2.325</v>
       </c>
       <c r="K249" t="b">
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0.8877846042645464</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
@@ -15181,25 +15181,25 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>-2.51</v>
+        <v>-2.33</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4892580000000001</v>
+        <v>1.008168</v>
       </c>
       <c r="H250" t="n">
-        <v>0</v>
+        <v>0.0001454122437109205</v>
       </c>
       <c r="I250" t="n">
-        <v>-3.28</v>
+        <v>-3.45</v>
       </c>
       <c r="J250" t="n">
-        <v>-1.74</v>
+        <v>-1.08</v>
       </c>
       <c r="K250" t="b">
         <v>1</v>
       </c>
       <c r="L250" t="n">
-        <v>1</v>
+        <v>0.9998545877562891</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
@@ -15240,25 +15240,25 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>0.155</v>
+        <v>0.365</v>
       </c>
       <c r="G251" t="n">
-        <v>0.4447800000000001</v>
+        <v>0.3261720000000003</v>
       </c>
       <c r="H251" t="n">
-        <v>0.6619082038308638</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5567499999999997</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="J251" t="n">
-        <v>1.005</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="K251" t="b">
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>0.6619082038308638</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
@@ -15299,25 +15299,25 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2.73</v>
+        <v>2.445</v>
       </c>
       <c r="G252" t="n">
-        <v>0.8450819999999997</v>
+        <v>0.7561259999999996</v>
       </c>
       <c r="H252" t="n">
-        <v>0.9996385977593061</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="I252" t="n">
-        <v>1.38325</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="J252" t="n">
-        <v>4.035</v>
+        <v>3.464999999999999</v>
       </c>
       <c r="K252" t="b">
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0.9996385977593061</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
@@ -15358,19 +15358,19 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>-3.815</v>
+        <v>-3.335</v>
       </c>
       <c r="G253" t="n">
-        <v>0.6894090000000004</v>
+        <v>0.6523440000000006</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
       </c>
       <c r="I253" t="n">
-        <v>-4.795</v>
+        <v>-4.17</v>
       </c>
       <c r="J253" t="n">
-        <v>-2.47</v>
+        <v>-2.04</v>
       </c>
       <c r="K253" t="b">
         <v>1</v>
@@ -15417,25 +15417,25 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="G254" t="n">
-        <v>0.3558240000000001</v>
+        <v>0.4966710000000001</v>
       </c>
       <c r="H254" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1449999999999999</v>
+        <v>-0.2439999999999999</v>
       </c>
       <c r="J254" t="n">
-        <v>1.055</v>
+        <v>1.698999999999999</v>
       </c>
       <c r="K254" t="b">
         <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
@@ -15476,25 +15476,25 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>1.335</v>
+        <v>1.19</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6078660000000005</v>
+        <v>0.6226919999999992</v>
       </c>
       <c r="H255" t="n">
-        <v>0.9799978492311001</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3</v>
+        <v>-0.2299999999999997</v>
       </c>
       <c r="J255" t="n">
-        <v>2.325</v>
+        <v>2.05</v>
       </c>
       <c r="K255" t="b">
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>0.9799978492311001</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
@@ -15535,19 +15535,19 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>-2.47</v>
+        <v>-2.555</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7042350000000001</v>
+        <v>0.5040839999999998</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>-3.445</v>
+        <v>-3.305</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.415</v>
+        <v>-1.735</v>
       </c>
       <c r="K256" t="b">
         <v>1</v>
@@ -15594,25 +15594,25 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>0.225</v>
+        <v>0.2949999999999999</v>
       </c>
       <c r="G257" t="n">
-        <v>0.3409980000000001</v>
+        <v>0.4892579999999997</v>
       </c>
       <c r="H257" t="n">
-        <v>0.7562103451984085</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.25</v>
+        <v>-0.5950000000000002</v>
       </c>
       <c r="J257" t="n">
-        <v>0.79</v>
+        <v>1.133999999999998</v>
       </c>
       <c r="K257" t="b">
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>0.7562103451984085</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
@@ -15653,25 +15653,25 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>2.765</v>
+        <v>2.545</v>
       </c>
       <c r="G258" t="n">
-        <v>0.6597570000000004</v>
+        <v>0.7783649999999999</v>
       </c>
       <c r="H258" t="n">
-        <v>0.9998924615550059</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="I258" t="n">
-        <v>1.5</v>
+        <v>1.235</v>
       </c>
       <c r="J258" t="n">
-        <v>3.789999999999999</v>
+        <v>3.925</v>
       </c>
       <c r="K258" t="b">
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>0.9998924615550059</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="M258" t="inlineStr">
         <is>
@@ -15712,19 +15712,19 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>-3.53</v>
+        <v>-3.785</v>
       </c>
       <c r="G259" t="n">
-        <v>0.5856270000000007</v>
+        <v>0.6449310000000007</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>-4.395</v>
+        <v>-4.77</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.325</v>
+        <v>-2.551000000000001</v>
       </c>
       <c r="K259" t="b">
         <v>1</v>
@@ -15771,25 +15771,25 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="G260" t="n">
-        <v>0.2742810000000002</v>
+        <v>0.3113460000000001</v>
       </c>
       <c r="H260" t="n">
-        <v>0.8984509466437177</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2200000000000002</v>
+        <v>0.004999999999999893</v>
       </c>
       <c r="J260" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.24</v>
       </c>
       <c r="K260" t="b">
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>0.8984509466437177</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
@@ -15830,25 +15830,25 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>0.05000000000000016</v>
+        <v>1.185</v>
       </c>
       <c r="G261" t="n">
-        <v>0.3706500000000001</v>
+        <v>0.5782140000000004</v>
       </c>
       <c r="H261" t="n">
-        <v>0.5473321858864028</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.165</v>
       </c>
       <c r="J261" t="n">
-        <v>0.6250000000000001</v>
+        <v>2.135</v>
       </c>
       <c r="K261" t="b">
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>0.5473321858864028</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
@@ -15889,19 +15889,19 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>-1.235</v>
+        <v>-2.38</v>
       </c>
       <c r="G262" t="n">
-        <v>0.1853249999999997</v>
+        <v>0.5485620000000001</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
       </c>
       <c r="I262" t="n">
-        <v>-1.66975</v>
+        <v>-3.275</v>
       </c>
       <c r="J262" t="n">
-        <v>-0.8252499999999997</v>
+        <v>-1.58</v>
       </c>
       <c r="K262" t="b">
         <v>1</v>
@@ -15948,25 +15948,25 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>0.3700000000000001</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="G263" t="n">
-        <v>0.4447800000000004</v>
+        <v>0.214977</v>
       </c>
       <c r="H263" t="n">
-        <v>0.7409638554216867</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.7600000000000002</v>
+        <v>-0.38</v>
       </c>
       <c r="J263" t="n">
-        <v>1.005</v>
+        <v>0.425</v>
       </c>
       <c r="K263" t="b">
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>0.7409638554216867</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
@@ -16007,25 +16007,25 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>0.5750000000000002</v>
+        <v>3.024999999999999</v>
       </c>
       <c r="G264" t="n">
-        <v>1.1008305</v>
+        <v>0.6745830000000014</v>
       </c>
       <c r="H264" t="n">
-        <v>0.6790017211703959</v>
+        <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.88975</v>
+        <v>1.725</v>
       </c>
       <c r="J264" t="n">
-        <v>1.925</v>
+        <v>4.175000000000001</v>
       </c>
       <c r="K264" t="b">
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>0.6790017211703959</v>
+        <v>1</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
@@ -16066,19 +16066,19 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>-2.145</v>
+        <v>-3.655</v>
       </c>
       <c r="G265" t="n">
-        <v>0.4151279999999997</v>
+        <v>0.7190610000000004</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
       </c>
       <c r="I265" t="n">
-        <v>-3.16</v>
+        <v>-4.665</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.055499999999999</v>
+        <v>-2.42</v>
       </c>
       <c r="K265" t="b">
         <v>1</v>
@@ -16125,25 +16125,25 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="G266" t="n">
-        <v>0.3261720000000003</v>
+        <v>0.3261720000000001</v>
       </c>
       <c r="H266" t="n">
-        <v>0.934146116191004</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.04349999999999962</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="J266" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="K266" t="b">
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>0.934146116191004</v>
+        <v>0.9335369707183484</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
@@ -16184,25 +16184,25 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>0.3150000000000002</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="G267" t="n">
-        <v>0.3558240000000006</v>
+        <v>0.3409980000000003</v>
       </c>
       <c r="H267" t="n">
-        <v>0.788676457005634</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.4300000000000002</v>
+        <v>-0.3717499999999999</v>
       </c>
       <c r="J267" t="n">
-        <v>0.8750000000000001</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K267" t="b">
         <v>0</v>
       </c>
       <c r="L267" t="n">
-        <v>0.788676457005634</v>
+        <v>0.8209395407625869</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
@@ -16243,25 +16243,25 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>-1.205</v>
+        <v>-1.2</v>
       </c>
       <c r="G268" t="n">
         <v>0.185325</v>
       </c>
       <c r="H268" t="n">
-        <v>9.236168837166343e-05</v>
+        <v>0</v>
       </c>
       <c r="I268" t="n">
-        <v>-1.59</v>
+        <v>-1.585</v>
       </c>
       <c r="J268" t="n">
-        <v>-0.805</v>
+        <v>-0.78</v>
       </c>
       <c r="K268" t="b">
         <v>1</v>
       </c>
       <c r="L268" t="n">
-        <v>0.9999076383116283</v>
+        <v>1</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
@@ -16302,25 +16302,25 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>0.2549999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="G269" t="n">
-        <v>0.5263230000000001</v>
+        <v>0.548562</v>
       </c>
       <c r="H269" t="n">
-        <v>0.6614944121178535</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.745</v>
+        <v>-0.765</v>
       </c>
       <c r="J269" t="n">
-        <v>1.07</v>
+        <v>1.105</v>
       </c>
       <c r="K269" t="b">
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>0.6614944121178535</v>
+        <v>0.655677269854645</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
@@ -16361,25 +16361,25 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="G270" t="n">
-        <v>0.785778</v>
+        <v>0.6597570000000001</v>
       </c>
       <c r="H270" t="n">
-        <v>0.7888611803823774</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5034999999999996</v>
+        <v>-0.5</v>
       </c>
       <c r="J270" t="n">
-        <v>2.58</v>
+        <v>2.561750000000002</v>
       </c>
       <c r="K270" t="b">
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>0.7888611803823774</v>
+        <v>0.7746998104065725</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
@@ -16420,25 +16420,25 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>-1.225</v>
+        <v>-1.145</v>
       </c>
       <c r="G271" t="n">
-        <v>0.6152789999999997</v>
+        <v>0.4373669999999997</v>
       </c>
       <c r="H271" t="n">
-        <v>0.006095871432529786</v>
+        <v>0.006951759005687803</v>
       </c>
       <c r="I271" t="n">
-        <v>-3.235</v>
+        <v>-3.095</v>
       </c>
       <c r="J271" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K271" t="b">
         <v>1</v>
       </c>
       <c r="L271" t="n">
-        <v>0.9939041285674702</v>
+        <v>0.9930482409943122</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
@@ -16479,25 +16479,25 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>0.4749999999999999</v>
+        <v>0.4750000000000002</v>
       </c>
       <c r="G272" t="n">
-        <v>0.4299540000000002</v>
+        <v>0.4077149999999997</v>
       </c>
       <c r="H272" t="n">
-        <v>0.8560808234845597</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.21</v>
+        <v>-0.196</v>
       </c>
       <c r="J272" t="n">
-        <v>1.105</v>
+        <v>1.065</v>
       </c>
       <c r="K272" t="b">
         <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>0.8560808234845597</v>
+        <v>0.8692743929038825</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
@@ -16538,25 +16538,25 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>1.3475</v>
+        <v>1.175</v>
       </c>
       <c r="G273" t="n">
-        <v>0.6560505000000001</v>
+        <v>0.8895600000000005</v>
       </c>
       <c r="H273" t="n">
-        <v>0.9662600076248571</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="I273" t="n">
-        <v>0.155</v>
+        <v>-0.2399999999999998</v>
       </c>
       <c r="J273" t="n">
-        <v>2.35</v>
+        <v>2.325</v>
       </c>
       <c r="K273" t="b">
         <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>0.9662600076248571</v>
+        <v>0.8884688090737241</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
@@ -16597,25 +16597,25 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>-2.57</v>
+        <v>-2.33</v>
       </c>
       <c r="G274" t="n">
-        <v>0.7487130000000004</v>
+        <v>1.008168</v>
       </c>
       <c r="H274" t="n">
-        <v>0</v>
+        <v>0.0001454122437109205</v>
       </c>
       <c r="I274" t="n">
-        <v>-3.49</v>
+        <v>-3.45</v>
       </c>
       <c r="J274" t="n">
-        <v>-1.305</v>
+        <v>-1.08</v>
       </c>
       <c r="K274" t="b">
         <v>1</v>
       </c>
       <c r="L274" t="n">
-        <v>1</v>
+        <v>0.9998545877562891</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
@@ -16656,25 +16656,25 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>0.4150000000000001</v>
+        <v>0.365</v>
       </c>
       <c r="G275" t="n">
-        <v>0.2891069999999996</v>
+        <v>0.3261720000000003</v>
       </c>
       <c r="H275" t="n">
-        <v>0.8112847884102173</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2499999999999999</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="J275" t="n">
-        <v>0.8899999999999999</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="K275" t="b">
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>0.8112847884102173</v>
+        <v>0.7827541078958848</v>
       </c>
       <c r="M275" t="inlineStr">
         <is>
@@ -16715,25 +16715,25 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2.56</v>
+        <v>2.445</v>
       </c>
       <c r="G276" t="n">
-        <v>0.630104999999999</v>
+        <v>0.7561259999999996</v>
       </c>
       <c r="H276" t="n">
-        <v>0.9998093785741518</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="I276" t="n">
-        <v>1.37</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="J276" t="n">
-        <v>3.41</v>
+        <v>3.464999999999999</v>
       </c>
       <c r="K276" t="b">
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0.9998093785741518</v>
+        <v>0.9784789879307838</v>
       </c>
       <c r="M276" t="inlineStr">
         <is>
@@ -16774,19 +16774,19 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>-3.475</v>
+        <v>-3.335</v>
       </c>
       <c r="G277" t="n">
-        <v>0.5633879999999998</v>
+        <v>0.6523440000000006</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
       </c>
       <c r="I277" t="n">
-        <v>-4.21</v>
+        <v>-4.17</v>
       </c>
       <c r="J277" t="n">
-        <v>-2.215</v>
+        <v>-2.04</v>
       </c>
       <c r="K277" t="b">
         <v>1</v>
@@ -16833,25 +16833,25 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="G278" t="n">
-        <v>0.2965199999999999</v>
+        <v>0.4966710000000001</v>
       </c>
       <c r="H278" t="n">
-        <v>0.9396043040610899</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.02474999999999986</v>
+        <v>-0.2439999999999999</v>
       </c>
       <c r="J278" t="n">
-        <v>1.675</v>
+        <v>1.698999999999999</v>
       </c>
       <c r="K278" t="b">
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0.9396043040610899</v>
+        <v>0.8363150867823765</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
@@ -16892,25 +16892,25 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="G279" t="n">
-        <v>0.5633879999999998</v>
+        <v>0.6226919999999992</v>
       </c>
       <c r="H279" t="n">
-        <v>0.9659840333217633</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1699999999999999</v>
+        <v>-0.2299999999999997</v>
       </c>
       <c r="J279" t="n">
-        <v>2.165</v>
+        <v>2.05</v>
       </c>
       <c r="K279" t="b">
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0.9659840333217633</v>
+        <v>0.9233644859813084</v>
       </c>
       <c r="M279" t="inlineStr">
         <is>
@@ -16951,19 +16951,19 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>-2.36</v>
+        <v>-2.555</v>
       </c>
       <c r="G280" t="n">
-        <v>0.5522685000000001</v>
+        <v>0.5040839999999998</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>-3.285</v>
+        <v>-3.305</v>
       </c>
       <c r="J280" t="n">
-        <v>-1.575</v>
+        <v>-1.735</v>
       </c>
       <c r="K280" t="b">
         <v>1</v>
@@ -17010,25 +17010,25 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>0.07999999999999996</v>
+        <v>0.2949999999999999</v>
       </c>
       <c r="G281" t="n">
-        <v>0.207564</v>
+        <v>0.4892579999999997</v>
       </c>
       <c r="H281" t="n">
-        <v>0.6405761888233252</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.335</v>
+        <v>-0.5950000000000002</v>
       </c>
       <c r="J281" t="n">
-        <v>0.4149999999999999</v>
+        <v>1.133999999999998</v>
       </c>
       <c r="K281" t="b">
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0.6405761888233252</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
@@ -17069,25 +17069,25 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>3.035</v>
+        <v>2.545</v>
       </c>
       <c r="G282" t="n">
-        <v>0.6523439999999999</v>
+        <v>0.7783649999999999</v>
       </c>
       <c r="H282" t="n">
-        <v>1</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="I282" t="n">
-        <v>1.72</v>
+        <v>1.235</v>
       </c>
       <c r="J282" t="n">
-        <v>4.2</v>
+        <v>3.925</v>
       </c>
       <c r="K282" t="b">
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>1</v>
+        <v>0.9994659546061415</v>
       </c>
       <c r="M282" t="inlineStr">
         <is>
@@ -17128,19 +17128,19 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>-3.645</v>
+        <v>-3.785</v>
       </c>
       <c r="G283" t="n">
-        <v>0.6894090000000004</v>
+        <v>0.6449310000000007</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
       </c>
       <c r="I283" t="n">
-        <v>-4.645</v>
+        <v>-4.77</v>
       </c>
       <c r="J283" t="n">
-        <v>-2.4</v>
+        <v>-2.551000000000001</v>
       </c>
       <c r="K283" t="b">
         <v>1</v>
@@ -17187,25 +17187,25 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G284" t="n">
-        <v>0.541149</v>
+        <v>0.3113460000000001</v>
       </c>
       <c r="H284" t="n">
-        <v>0.8430864836872087</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.235</v>
+        <v>0.004999999999999893</v>
       </c>
       <c r="J284" t="n">
-        <v>2.698999999999996</v>
+        <v>2.24</v>
       </c>
       <c r="K284" t="b">
         <v>0</v>
       </c>
       <c r="L284" t="n">
-        <v>0.8430864836872087</v>
+        <v>0.9500089589679269</v>
       </c>
       <c r="M284" t="inlineStr">
         <is>
@@ -17246,25 +17246,25 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>1.165</v>
+        <v>1.185</v>
       </c>
       <c r="G285" t="n">
-        <v>0.6523439999999999</v>
+        <v>0.5782140000000004</v>
       </c>
       <c r="H285" t="n">
-        <v>0.8871051268772656</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5147499999999996</v>
+        <v>-0.165</v>
       </c>
       <c r="J285" t="n">
-        <v>2.045</v>
+        <v>2.135</v>
       </c>
       <c r="K285" t="b">
         <v>0</v>
       </c>
       <c r="L285" t="n">
-        <v>0.8871051268772656</v>
+        <v>0.9385414800215015</v>
       </c>
       <c r="M285" t="inlineStr">
         <is>
@@ -17305,19 +17305,19 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>-2.585</v>
+        <v>-2.38</v>
       </c>
       <c r="G286" t="n">
-        <v>0.4966709999999999</v>
+        <v>0.5485620000000001</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
       </c>
       <c r="I286" t="n">
-        <v>-3.325</v>
+        <v>-3.275</v>
       </c>
       <c r="J286" t="n">
-        <v>-1.765</v>
+        <v>-1.58</v>
       </c>
       <c r="K286" t="b">
         <v>1</v>
@@ -17364,25 +17364,25 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>0.2700000000000001</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="G287" t="n">
-        <v>0.511497</v>
+        <v>0.214977</v>
       </c>
       <c r="H287" t="n">
-        <v>0.7131020196789228</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.6500000000000001</v>
+        <v>-0.38</v>
       </c>
       <c r="J287" t="n">
-        <v>1.12</v>
+        <v>0.425</v>
       </c>
       <c r="K287" t="b">
         <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>0.7131020196789228</v>
+        <v>0.6222899122021143</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
@@ -17423,25 +17423,25 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>2.575</v>
+        <v>3.024999999999999</v>
       </c>
       <c r="G288" t="n">
-        <v>0.800603999999999</v>
+        <v>0.6745830000000014</v>
       </c>
       <c r="H288" t="n">
-        <v>0.9994821336095288</v>
+        <v>1</v>
       </c>
       <c r="I288" t="n">
-        <v>1.27</v>
+        <v>1.725</v>
       </c>
       <c r="J288" t="n">
-        <v>3.994749999999998</v>
+        <v>4.175000000000001</v>
       </c>
       <c r="K288" t="b">
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>0.9994821336095288</v>
+        <v>1</v>
       </c>
       <c r="M288" t="inlineStr">
         <is>
@@ -17482,19 +17482,19 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>-3.815</v>
+        <v>-3.655</v>
       </c>
       <c r="G289" t="n">
-        <v>0.6523439999999993</v>
+        <v>0.7190610000000004</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
       </c>
       <c r="I289" t="n">
-        <v>-4.77</v>
+        <v>-4.665</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.645250000000001</v>
+        <v>-2.42</v>
       </c>
       <c r="K289" t="b">
         <v>1</v>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_edge_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_edge_profile_summary.xlsx
@@ -579,7 +579,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11553,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12792,7 +12792,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12910,7 +12910,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13205,7 +13205,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13795,7 +13795,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14031,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14208,7 +14208,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14267,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14326,7 +14326,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14385,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14444,7 +14444,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15447,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -15978,7 +15978,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16155,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16273,7 +16273,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16568,7 +16568,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16627,7 +16627,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -17335,7 +17335,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
     </row>
